--- a/src/attributions/attributions_saliency_traj_171.xlsx
+++ b/src/attributions/attributions_saliency_traj_171.xlsx
@@ -999,4554 +999,4554 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4248493909835815</v>
+        <v>0.005558044649660587</v>
       </c>
       <c r="B2" t="n">
-        <v>0.005426384508609772</v>
+        <v>0.005325357429683208</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06685727834701538</v>
+        <v>0.007931534200906754</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06719401478767395</v>
+        <v>0.004527694545686245</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1809352040290833</v>
+        <v>0.001301647280342877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03432032093405724</v>
+        <v>0.0003888065693899989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1818058490753174</v>
+        <v>0.01161039806902409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005452326498925686</v>
+        <v>0.006633047945797443</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07488946616649628</v>
+        <v>0.001781387254595757</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3685595393180847</v>
+        <v>0.003730452619493008</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04812284559011459</v>
+        <v>0.007008432876318693</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1490614861249924</v>
+        <v>0.012846021912992</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02903063967823982</v>
+        <v>0.01282929535955191</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08878291398286819</v>
+        <v>0.00575112272053957</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1162822470068932</v>
+        <v>0.001098677632398903</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1365156769752502</v>
+        <v>0.01917317509651184</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04161360859870911</v>
+        <v>0.006187227088958025</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06853383034467697</v>
+        <v>0.003886034712195396</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07860977202653885</v>
+        <v>7.757515413686633e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02351647615432739</v>
+        <v>0.005277061834931374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01757956854999065</v>
+        <v>0.0003009005449712276</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1475021094083786</v>
+        <v>0.001842841622419655</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08852187544107437</v>
+        <v>0.002648503752425313</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00268237479031086</v>
+        <v>0.001419908367097378</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04849956184625626</v>
+        <v>0.00350255100056529</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.014998534694314</v>
+        <v>0.00195011030882597</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03048841841518879</v>
+        <v>0.002160461153835058</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.06745932996273041</v>
+        <v>0.006252181716263294</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0397246889770031</v>
+        <v>0.008100263774394989</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.08531303703784943</v>
+        <v>4.615040961652994e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01331600733101368</v>
+        <v>0.003174552926793694</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.004415024071931839</v>
+        <v>0.005851590074598789</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.06694962084293365</v>
+        <v>0.001647402066737413</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02857221849262714</v>
+        <v>0.01131122931838036</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.001435991376638412</v>
+        <v>0.003841924481093884</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.06716234982013702</v>
+        <v>0.004321728367358446</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01555701065808535</v>
+        <v>0.001248405897058547</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05141583457589149</v>
+        <v>0.003314318833872676</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.04101992025971413</v>
+        <v>0.001214155461639166</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03993861377239227</v>
+        <v>0.001593698631040752</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.007969466038048267</v>
+        <v>0.0005015871720388532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.005164063069969416</v>
+        <v>0.001699542859569192</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.03189869225025177</v>
+        <v>0.006222306750714779</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.002351120114326477</v>
+        <v>0.002245594281703234</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.004755687434226274</v>
+        <v>0.001342944102361798</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.2613694369792938</v>
+        <v>0.006846668664366007</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2067509293556213</v>
+        <v>0.01422477327287197</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.06644183397293091</v>
+        <v>0.002999517833814025</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.05530958622694016</v>
+        <v>0.002637577708810568</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.009351268410682678</v>
+        <v>0.0077564911916852</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.02139375172555447</v>
+        <v>0.006456438452005386</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1125271916389465</v>
+        <v>0.006364623084664345</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.04361841082572937</v>
+        <v>0.005563444457948208</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.04672686383128166</v>
+        <v>0.002192513318732381</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.125167191028595</v>
+        <v>0.008640982210636139</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.229104071855545</v>
+        <v>0.003685184754431248</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0958673432469368</v>
+        <v>0.005025935359299183</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.04468918219208717</v>
+        <v>0.001566986553370953</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.07916117459535599</v>
+        <v>0.002464107470586896</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.04337534308433533</v>
+        <v>0.004740552045404911</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.02928810007870197</v>
+        <v>0.0003740359679795802</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.08980218321084976</v>
+        <v>0.0002069334732368588</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.07147031277418137</v>
+        <v>0.0002662439364939928</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.05247445404529572</v>
+        <v>0.0005720459157600999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1309839487075806</v>
+        <v>0.001395998406223953</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.04316170513629913</v>
+        <v>0.005734207108616829</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01712715998291969</v>
+        <v>0.007299265824258327</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.003471846925094724</v>
+        <v>0.0006768988678231835</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.03335399925708771</v>
+        <v>0.001325662364251912</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.007000261917710304</v>
+        <v>0.001930756727233529</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.02332337573170662</v>
+        <v>0.002903352491557598</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.003247030079364777</v>
+        <v>0.002959685865789652</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1385784298181534</v>
+        <v>0.00222492846660316</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.007688568904995918</v>
+        <v>0.0003671217709779739</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.06142471358180046</v>
+        <v>0.001964180963113904</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1339024305343628</v>
+        <v>0.001238276250660419</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03764727339148521</v>
+        <v>0.005588729865849018</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.01641333475708961</v>
+        <v>0.002208790509030223</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.06986048817634583</v>
+        <v>0.000504650641232729</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.04945807158946991</v>
+        <v>0.003149119205772877</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.04932324215769768</v>
+        <v>0.00118345650844276</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.08389125019311905</v>
+        <v>0.0006243563257157803</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.02830179966986179</v>
+        <v>0.006539796479046345</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.005694850347936153</v>
+        <v>0.00272323889657855</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.03407266736030579</v>
+        <v>0.0001704826718196273</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01807448454201221</v>
+        <v>0.002064733766019344</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.04426110908389091</v>
+        <v>0.00191663927398622</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0497516468167305</v>
+        <v>0.002448736457154155</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.008224081248044968</v>
+        <v>0.002117620315402746</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.01672617718577385</v>
+        <v>0.0007883204962126911</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.06392452865839005</v>
+        <v>0.002075579483062029</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01985891535878181</v>
+        <v>0.01401727087795734</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.02729528024792671</v>
+        <v>0.002207472687587142</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.05832860991358757</v>
+        <v>0.002745805773884058</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1358741074800491</v>
+        <v>0.0002813389874063432</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.04409999400377274</v>
+        <v>0.006533748935908079</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.04331258311867714</v>
+        <v>0.001077386667020619</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.03225567191839218</v>
+        <v>0.01368078403174877</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.009730048477649689</v>
+        <v>0.001115303253754973</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.06432253867387772</v>
+        <v>0.0002013240591622889</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0435592383146286</v>
+        <v>0.006974750198423862</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01245053485035896</v>
+        <v>0.003004960250109434</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.01145287975668907</v>
+        <v>0.000769277336075902</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.02029244601726532</v>
+        <v>0.0008432759786956012</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.05172766372561455</v>
+        <v>0.003340156283229589</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.03881640732288361</v>
+        <v>0.001394433900713921</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.01924766227602959</v>
+        <v>0.002618235535919666</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.01941749639809132</v>
+        <v>0.0004751372034661472</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08411087840795517</v>
+        <v>0.002674099989235401</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.01371354609727859</v>
+        <v>0.007518549915403128</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01439879089593887</v>
+        <v>0.004395925439894199</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.002838257700204849</v>
+        <v>0.01312749274075031</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1275856196880341</v>
+        <v>0.005417726002633572</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.187629371881485</v>
+        <v>0.009442338719964027</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.01672225818037987</v>
+        <v>0.00204476504586637</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.07723185420036316</v>
+        <v>0.00651751272380352</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0877348780632019</v>
+        <v>0.001622434239834547</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.03703194856643677</v>
+        <v>0.0003486699424684048</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.003472937270998955</v>
+        <v>0.001448465744033456</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.01971982792019844</v>
+        <v>0.0001637457171455026</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04907514527440071</v>
+        <v>0.0007174492347985506</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.01232560351490974</v>
+        <v>0.0005857087671756744</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1003331691026688</v>
+        <v>0.000120447133667767</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.005570352077484131</v>
+        <v>0.004064890090376139</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.05229188501834869</v>
+        <v>0.005886472761631012</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.03340987116098404</v>
+        <v>0.0006798417307436466</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.04873554781079292</v>
+        <v>0.000305518158711493</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.05684682726860046</v>
+        <v>0.008136779069900513</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.07066704332828522</v>
+        <v>7.254420779645443e-06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.04408949986100197</v>
+        <v>0.002663332736119628</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.009102235548198223</v>
+        <v>0.003521277336403728</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.02620180323719978</v>
+        <v>0.009683133102953434</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.05021036416292191</v>
+        <v>0.001524165971204638</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.05003555864095688</v>
+        <v>0.001909309532493353</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.003600064665079117</v>
+        <v>0.003172161057591438</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.08716858923435211</v>
+        <v>0.002395901130512357</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0305892676115036</v>
+        <v>0.006935073062777519</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.03077667579054832</v>
+        <v>0.002466228324919939</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.01579600945115089</v>
+        <v>0.005597726441919804</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.06741391122341156</v>
+        <v>0.004778425209224224</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.09260641038417816</v>
+        <v>0.001032358733937144</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.02457833662629128</v>
+        <v>0.0008026884170249104</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.02838608995079994</v>
+        <v>0.001871324493549764</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.01095192134380341</v>
+        <v>0.001336695393547416</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.02906248345971107</v>
+        <v>0.001450382871553302</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.082107774913311</v>
+        <v>0.00904449075460434</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.02682101354002953</v>
+        <v>0.001046112272888422</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03951523080468178</v>
+        <v>0.003157422877848148</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.007302477024495602</v>
+        <v>0.001754731638357043</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.01906326040625572</v>
+        <v>0.001743323868140578</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.007649717852473259</v>
+        <v>0.0007573690381832421</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.03372672572731972</v>
+        <v>0.01306599099189043</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.03336546570062637</v>
+        <v>0.001619691145606339</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.07400400936603546</v>
+        <v>0.0006908613722771406</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04004531353712082</v>
+        <v>0.006690490990877151</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.02265459485352039</v>
+        <v>0.001713691046461463</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.02412065118551254</v>
+        <v>0.001072602462954819</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01400484889745712</v>
+        <v>0.0002878554514609277</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.04293405637145042</v>
+        <v>0.002491005230695009</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.04893834888935089</v>
+        <v>0.002064098371192813</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.003989323042333126</v>
+        <v>0.002073645126074553</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.00615295534953475</v>
+        <v>0.001008080667816103</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.04546952247619629</v>
+        <v>9.694707114249468e-05</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03585754334926605</v>
+        <v>0.004981275647878647</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.07261873036623001</v>
+        <v>0.003632322419434786</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.06890660524368286</v>
+        <v>0.0008413809118792415</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.006836632266640663</v>
+        <v>0.003542883088812232</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.08750332146883011</v>
+        <v>0.00241996836848557</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.04954145103693008</v>
+        <v>0.001288176397792995</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.04411802068352699</v>
+        <v>0.01382676232606173</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.03489383310079575</v>
+        <v>0.001253030262887478</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.05483264103531837</v>
+        <v>0.0003164082299917936</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.06327609717845917</v>
+        <v>0.003497547004371881</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.0153557937592268</v>
+        <v>0.00746481167152524</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.06163592264056206</v>
+        <v>0.004641697742044926</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.1563961356878281</v>
+        <v>0.01347914338111877</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.1293284147977829</v>
+        <v>0.006961585953831673</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.02450312487781048</v>
+        <v>0.01629700511693954</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.005774820223450661</v>
+        <v>0.0002143791643902659</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.06791559606790543</v>
+        <v>0.009317106567323208</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.03786887973546982</v>
+        <v>0.001928219338878989</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.02467397972941399</v>
+        <v>0.003551265690475702</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0720047801733017</v>
+        <v>0.002288048854097724</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0003005352336913347</v>
+        <v>0.007125611416995525</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.06228996068239212</v>
+        <v>0.003320014569908381</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.02725188247859478</v>
+        <v>0.01107970718294382</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.007337957620620728</v>
+        <v>0.005152270663529634</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0199426282197237</v>
+        <v>0.01495635695755482</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.04061219841241837</v>
+        <v>0.00043427714263089</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01597326062619686</v>
+        <v>0.004931834526360035</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1192263290286064</v>
+        <v>0.02568211033940315</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01087657175958157</v>
+        <v>0.004961057566106319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06573143601417542</v>
+        <v>0.00407902617007494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006806658115237951</v>
+        <v>0.003187666414305568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1343320310115814</v>
+        <v>0.02795251086354256</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01846985891461372</v>
+        <v>0.004049989860504866</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04597194120287895</v>
+        <v>0.01143054012209177</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02673769183456898</v>
+        <v>0.009410938248038292</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03289203718304634</v>
+        <v>0.004160253796726465</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07750372588634491</v>
+        <v>0.03727478533983231</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003671904094517231</v>
+        <v>0.006193699780851603</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06439553946256638</v>
+        <v>0.01477293111383915</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0129165593534708</v>
+        <v>0.004881772678345442</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1091495007276535</v>
+        <v>0.02899268083274364</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008467316627502441</v>
+        <v>0.001549237174913287</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03712862730026245</v>
+        <v>0.001691178767941892</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01831871643662453</v>
+        <v>0.01486095227301121</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00986658688634634</v>
+        <v>0.0007126074051484466</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002284097019582987</v>
+        <v>0.006421828642487526</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007391512044705451</v>
+        <v>0.003090228652581573</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005425640381872654</v>
+        <v>0.01027728244662285</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01794205605983734</v>
+        <v>0.001797223696485162</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01155112311244011</v>
+        <v>0.005756781436502934</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009537631645798683</v>
+        <v>0.0006430518114939332</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006617922335863113</v>
+        <v>0.007891564629971981</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001245073974132538</v>
+        <v>0.0001519108191132545</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01335809007287025</v>
+        <v>0.01198392268270254</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03338361158967018</v>
+        <v>0.001956802327185869</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.007337841205298901</v>
+        <v>0.001475003897212446</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01798973977565765</v>
+        <v>0.008424470201134682</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.007197478320449591</v>
+        <v>0.008748388849198818</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01346013601869345</v>
+        <v>0.001088008284568787</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.004216508474200964</v>
+        <v>0.008767181076109409</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.01775554567575455</v>
+        <v>0.01597553491592407</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.007981406524777412</v>
+        <v>0.009749540127813816</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.007891811430454254</v>
+        <v>0.002131510758772492</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01174231059849262</v>
+        <v>0.008301503956317902</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01175276190042496</v>
+        <v>0.001035102177411318</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.003549146000295877</v>
+        <v>0.003391220234334469</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.04088872671127319</v>
+        <v>0.007146887946873903</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.02665421366691589</v>
+        <v>0.009563758969306946</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.005031668581068516</v>
+        <v>0.005460652988404036</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.008715636096894741</v>
+        <v>0.01505711674690247</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.007151496596634388</v>
+        <v>0.007055689115077257</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.001259590499103069</v>
+        <v>0.007462399080395699</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.05603548511862755</v>
+        <v>0.04995208978652954</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.01663429290056229</v>
+        <v>0.0009551963303238153</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02650869637727737</v>
+        <v>0.008280843496322632</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.01004885230213404</v>
+        <v>0.00922868587076664</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1201284229755402</v>
+        <v>0.033430065959692</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01897103525698185</v>
+        <v>0.001101248664781451</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.01127333752810955</v>
+        <v>0.005833873059600592</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.02363672852516174</v>
+        <v>0.005513665266335011</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.01143377833068371</v>
+        <v>0.002566854003816843</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.028066610917449</v>
+        <v>0.01904758810997009</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.000784013420343399</v>
+        <v>0.001007417449727654</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.03250623494386673</v>
+        <v>0.007767899893224239</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.03699168935418129</v>
+        <v>0.01399008836597204</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.01331242360174656</v>
+        <v>0.003739425912499428</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.001183012034744024</v>
+        <v>0.009244278073310852</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.002759564435109496</v>
+        <v>0.002797908615320921</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.003503839485347271</v>
+        <v>0.0106681976467371</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01719536818563938</v>
+        <v>0.0004054293967783451</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.02834736928343773</v>
+        <v>0.006664903368800879</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01048343256115913</v>
+        <v>0.004255940206348896</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0007090698927640915</v>
+        <v>0.003741926047950983</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.007147272117435932</v>
+        <v>0.00305237784050405</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.009258201345801353</v>
+        <v>0.001363237504847348</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.004245907999575138</v>
+        <v>0.01258192956447601</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.009586194530129433</v>
+        <v>0.006757368333637714</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.007912566885352135</v>
+        <v>0.002463100012391806</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.005486417561769485</v>
+        <v>0.002533954801037908</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.04002903401851654</v>
+        <v>0.02161193452775478</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.004955284297466278</v>
+        <v>0.002476246794685721</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.00100594200193882</v>
+        <v>0.009080559946596622</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.02606517449021339</v>
+        <v>0.004026767332106829</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.05811935663223267</v>
+        <v>0.02155085280537605</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.001065236865542829</v>
+        <v>0.006750828586518764</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.00848754309117794</v>
+        <v>0.00534181809052825</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.01009355951100588</v>
+        <v>0.00458114966750145</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.001699871849268675</v>
+        <v>0.0004734278190881014</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.02341258525848389</v>
+        <v>0.01086340472102165</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0005369405262172222</v>
+        <v>0.002193853724747896</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.01477848552167416</v>
+        <v>0.003029823303222656</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.00521452259272337</v>
+        <v>0.002353545976802707</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.02008785307407379</v>
+        <v>0.00917478185147047</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.007321438752114773</v>
+        <v>0.005722237750887871</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01063703373074532</v>
+        <v>0.0004559911030810326</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.00274146138690412</v>
+        <v>0.003742642933502793</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.02329888381063938</v>
+        <v>0.004362126812338829</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0001019695773720741</v>
+        <v>0.0150730311870575</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.007712764665484428</v>
+        <v>0.003884109202772379</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.02384078316390514</v>
+        <v>0.01201071124523878</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.04759321734309196</v>
+        <v>0.003647342324256897</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.007386214565485716</v>
+        <v>0.01670088618993759</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.003518817480653524</v>
+        <v>0.003425086848437786</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.02031507156789303</v>
+        <v>0.001069286605343223</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.005690068937838078</v>
+        <v>0.00242387899197638</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.001696418737992644</v>
+        <v>0.002183874603360891</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0176678616553545</v>
+        <v>0.01084888353943825</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.007845913991332054</v>
+        <v>0.003193334210664034</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.01829205080866814</v>
+        <v>0.0009018628625199199</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0006623652298003435</v>
+        <v>0.001954833511263132</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.02774197608232498</v>
+        <v>0.009327059611678123</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001562111079692841</v>
+        <v>0.00255931681022048</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.01479605492204428</v>
+        <v>0.0004234711523167789</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.005676271393895149</v>
+        <v>0.002397667383775115</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0252744872123003</v>
+        <v>0.00442351121455431</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.04032697528600693</v>
+        <v>0.0007136673666536808</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.01495604403316975</v>
+        <v>0.002505435142666101</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.02602645568549633</v>
+        <v>0.005126467905938625</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.01197344064712524</v>
+        <v>0.006233669817447662</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.006388046313077211</v>
+        <v>0.007382216397672892</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.005362591706216335</v>
+        <v>0.008662424981594086</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0641620010137558</v>
+        <v>0.004932004492729902</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.01091860886663198</v>
+        <v>0.004802694078534842</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0103189293295145</v>
+        <v>0.00523253483697772</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.004012535326182842</v>
+        <v>0.0004405034414958209</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.006629772484302521</v>
+        <v>0.00520477956160903</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.009304966777563095</v>
+        <v>0.01204807311296463</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.008670808747410774</v>
+        <v>0.002771452767774463</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.008897281251847744</v>
+        <v>0.005966305732727051</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.009363044053316116</v>
+        <v>0.001472242292948067</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.004002101719379425</v>
+        <v>0.001881615025922656</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.006474959198385477</v>
+        <v>0.003424773691222072</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.003973867278546095</v>
+        <v>0.001142307068221271</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.008897460997104645</v>
+        <v>0.002487079473212361</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0077506173402071</v>
+        <v>0.0001338780857622623</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.009186690673232079</v>
+        <v>0.006665945984423161</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01274121459573507</v>
+        <v>0.002451073843985796</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.02117181196808815</v>
+        <v>0.00420826394110918</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.001421207562088966</v>
+        <v>0.006386666558682919</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.00385150290094316</v>
+        <v>0.003170247888192534</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.005867777857929468</v>
+        <v>0.001277395291253924</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.003471310017630458</v>
+        <v>0.002817376051098108</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.006313298363238573</v>
+        <v>0.003476971760392189</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.01331136282533407</v>
+        <v>0.0007688121404498816</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0009031752124428749</v>
+        <v>0.001052931183949113</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01130940765142441</v>
+        <v>0.002861999440938234</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.008133695460855961</v>
+        <v>0.001352670602500439</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.009709872305393219</v>
+        <v>0.0007387035875581205</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.002312285359948874</v>
+        <v>0.00244730687700212</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.005971692036837339</v>
+        <v>0.004493142012506723</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.003172371303662658</v>
+        <v>0.00369599019177258</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.01186656579375267</v>
+        <v>0.006556707434356213</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.02222821488976479</v>
+        <v>0.001921179122291505</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.01299150008708239</v>
+        <v>0.0007817590376362205</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01234028674662113</v>
+        <v>0.01177413947880268</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01388144120573997</v>
+        <v>0.005064438562840223</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.01448102481663227</v>
+        <v>0.005049846135079861</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.01654353365302086</v>
+        <v>0.002865252085030079</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.01654620468616486</v>
+        <v>0.002212580060586333</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0003754686331376433</v>
+        <v>0.001648349454626441</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.01633841171860695</v>
+        <v>0.01183850318193436</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0003168587572872639</v>
+        <v>0.002215508371591568</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01933982223272324</v>
+        <v>0.0008272491977550089</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.003143371548503637</v>
+        <v>0.00348653132095933</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.02231099642813206</v>
+        <v>0.00794819463044405</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.005395581014454365</v>
+        <v>0.006440518889576197</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01038694102317095</v>
+        <v>0.00118725118227303</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.003482565982267261</v>
+        <v>0.001245203195139766</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.006197696086019278</v>
+        <v>0.0001329733058810234</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01589727215468884</v>
+        <v>0.01173348259180784</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.01182234659790993</v>
+        <v>0.0003295496571809053</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.0471169576048851</v>
+        <v>0.009990964084863663</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.009131486527621746</v>
+        <v>0.005441811867058277</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.02661224268376827</v>
+        <v>0.005464750807732344</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.009435266256332397</v>
+        <v>0.00250954320654273</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.01213759556412697</v>
+        <v>0.007271240465342999</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.002907988149672747</v>
+        <v>0.0003414069069549441</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0195883996784687</v>
+        <v>0.005645942874252796</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.009487686678767204</v>
+        <v>0.008894535712897778</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.01876481249928474</v>
+        <v>0.001578171737492085</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.0343666784465313</v>
+        <v>0.01453298795968294</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04455256834626198</v>
+        <v>0.006907068192958832</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.02128646709024906</v>
+        <v>0.02084900811314583</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.004538098350167274</v>
+        <v>0.01810940727591515</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.01888342946767807</v>
+        <v>0.01098070293664932</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.008897462859749794</v>
+        <v>0.002670160960406065</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.005006310530006886</v>
+        <v>0.0001502205268479884</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.005193168763071299</v>
+        <v>0.0007364225457422435</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.01507905218750238</v>
+        <v>0.006003821268677711</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.02436686679720879</v>
+        <v>0.004183925222605467</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.07698328793048859</v>
+        <v>0.01371943112462759</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.01278604101389647</v>
+        <v>0.004525515250861645</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.01811540126800537</v>
+        <v>0.009032430127263069</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.01009094715118408</v>
+        <v>0.005238274578005075</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0005147927440702915</v>
+        <v>0.001359770307317376</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.007753857411444187</v>
+        <v>4.820560207008384e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06456597149372101</v>
+        <v>0.0001408988609910011</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007068997714668512</v>
+        <v>4.538031134870835e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02591192722320557</v>
+        <v>4.411731424625032e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0119650000706315</v>
+        <v>6.760993710486218e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03835391253232956</v>
+        <v>0.0001287589402636513</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004953915718942881</v>
+        <v>2.890677933464758e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01912180706858635</v>
+        <v>5.660087845171802e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007178876549005508</v>
+        <v>4.119281584280543e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01101733930408955</v>
+        <v>3.159440893796273e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06034954637289047</v>
+        <v>0.0001256211980944499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002318047918379307</v>
+        <v>8.210778469219804e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01963204331696033</v>
+        <v>0.0001233067887369543</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00588435772806406</v>
+        <v>1.099334622267634e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03337590768933296</v>
+        <v>0.0001627274323254824</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001102714682929218</v>
+        <v>2.819745895976666e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004341600462794304</v>
+        <v>2.363874955335632e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007398989517241716</v>
+        <v>5.232654075371101e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001659966073930264</v>
+        <v>1.765938759490382e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006383803673088551</v>
+        <v>3.654855754575692e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002712959190830588</v>
+        <v>5.645178134727757e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008684295229613781</v>
+        <v>9.665814104664605e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005675442516803741</v>
+        <v>6.863060207251692e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003616258502006531</v>
+        <v>5.42997986485716e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002361355349421501</v>
+        <v>3.324453791719861e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008461222983896732</v>
+        <v>2.645247150212526e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004554076585918665</v>
+        <v>1.097143831430003e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001270783133804798</v>
+        <v>9.773743840923999e-06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002042595064267516</v>
+        <v>4.592124241753481e-06</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0005342777003534138</v>
+        <v>1.034057640936226e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002035137731581926</v>
+        <v>4.810315294889733e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001426767557859421</v>
+        <v>1.869263360276818e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001537665608339012</v>
+        <v>7.55945875425823e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001482749357819557</v>
+        <v>6.547068551299162e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.003018959891051054</v>
+        <v>9.905698971124366e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001386261312291026</v>
+        <v>2.060181577689946e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01023957878351212</v>
+        <v>1.782355320756324e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.006586391013115644</v>
+        <v>1.781484752427787e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0005273108836263418</v>
+        <v>1.234881437994773e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002890016650781035</v>
+        <v>8.947930837166496e-06</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001734272693283856</v>
+        <v>1.718153725960292e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.009210530668497086</v>
+        <v>2.514359039196279e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003441906534135342</v>
+        <v>5.007239451515488e-06</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004804295487701893</v>
+        <v>4.147937215748243e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.008239259943366051</v>
+        <v>1.911831714096479e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001638565096072853</v>
+        <v>2.942425999208353e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0354093611240387</v>
+        <v>9.419442358193919e-05</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.005266210064291954</v>
+        <v>4.742948658531532e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.005164443980902433</v>
+        <v>2.495328226359561e-05</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.006273670587688684</v>
+        <v>7.492617442039773e-05</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.01850085891783237</v>
+        <v>0.0001361934118904173</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.009132888168096542</v>
+        <v>8.057718332565855e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008669763803482056</v>
+        <v>4.004406946478412e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.009727814234793186</v>
+        <v>1.110164885176346e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.004456254653632641</v>
+        <v>2.753328953986056e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01353685278445482</v>
+        <v>1.682201218500268e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.01521283946931362</v>
+        <v>3.530141111696139e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.909509051591158e-05</v>
+        <v>4.206981975585222e-05</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004293766804039478</v>
+        <v>6.824578304076567e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.00764347892254591</v>
+        <v>2.037657759501599e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00103641499299556</v>
+        <v>3.249399014748633e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.007600895594805479</v>
+        <v>6.217155896592885e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.004953298717737198</v>
+        <v>2.3116976080928e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.003648941870778799</v>
+        <v>2.529863195377402e-06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.009061484597623348</v>
+        <v>3.754279168788344e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005125902127474546</v>
+        <v>2.888285598601215e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0007418112363666296</v>
+        <v>2.893825512728654e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003895638510584831</v>
+        <v>1.137665458372794e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001745052519254386</v>
+        <v>1.305038131249603e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00643534492701292</v>
+        <v>1.042304666043492e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004223193041980267</v>
+        <v>2.154441426682752e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.006076836958527565</v>
+        <v>2.272351048304699e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0006236627232283354</v>
+        <v>1.827834785217419e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02139545418322086</v>
+        <v>4.983467442798428e-05</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.007405050564557314</v>
+        <v>4.681047357735224e-06</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001831521280109882</v>
+        <v>1.452355172659736e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003860750701278448</v>
+        <v>1.464371052861679e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.008758878335356712</v>
+        <v>4.780425661010668e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.002158742863684893</v>
+        <v>5.070967745268717e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.003087135730311275</v>
+        <v>1.701347719063051e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.00420304061844945</v>
+        <v>2.161178963433485e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001413146266713738</v>
+        <v>5.030924512539059e-07</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.01082334760576487</v>
+        <v>4.774331682710908e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.004626153036952019</v>
+        <v>1.794170202629175e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004069133196026087</v>
+        <v>1.778809382813051e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.002953908639028668</v>
+        <v>3.901857780874707e-06</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.004073872696608305</v>
+        <v>2.573188976384699e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.003835247363895178</v>
+        <v>2.322097770957043e-06</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.003503481391817331</v>
+        <v>5.662661237693101e-07</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.00492109265178442</v>
+        <v>5.155182407179382e-06</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.01395374070852995</v>
+        <v>7.29452494852012e-06</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.002933094277977943</v>
+        <v>1.780951060936786e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0008635742124170065</v>
+        <v>5.348988634068519e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0178051833063364</v>
+        <v>5.074865475762635e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.007104138378053904</v>
+        <v>1.528007123852149e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.01674219407141209</v>
+        <v>8.441019417659845e-06</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.01248999871313572</v>
+        <v>4.349370283307508e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.009332317858934402</v>
+        <v>4.062975131091662e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.00285971537232399</v>
+        <v>2.474676875863224e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.001394433784298599</v>
+        <v>1.051001891028136e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0104504032060504</v>
+        <v>3.978031963924877e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.004415910691022873</v>
+        <v>2.397680873400532e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.006889781914651394</v>
+        <v>2.544967719586566e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.002180944895371795</v>
+        <v>4.36019035987556e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.003710493911057711</v>
+        <v>3.637559711933136e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.004052304197102785</v>
+        <v>9.928098734235391e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.006514918524771929</v>
+        <v>7.369994818873238e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.00414577592164278</v>
+        <v>9.486474482400808e-06</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.006174941547214985</v>
+        <v>1.90126957022585e-06</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.01096299476921558</v>
+        <v>8.868679287843406e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.004130481742322445</v>
+        <v>7.183593697845936e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0129368482157588</v>
+        <v>1.833040369092487e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.02230158448219299</v>
+        <v>1.108427204599138e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.01217122562229633</v>
+        <v>8.655320561956614e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.005670794285833836</v>
+        <v>8.869717930792831e-06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.008919057436287403</v>
+        <v>5.592458910541609e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.01560742594301701</v>
+        <v>3.23667045449838e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002948121633380651</v>
+        <v>1.192741365230177e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.00653162132948637</v>
+        <v>4.332764001446776e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.003035357221961021</v>
+        <v>6.935068086022511e-06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.003401614492759109</v>
+        <v>2.806700103974435e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.002526151947677135</v>
+        <v>2.403358303126879e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.004364714492112398</v>
+        <v>1.044940654537641e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.004089398309588432</v>
+        <v>1.758862708811648e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.007529404945671558</v>
+        <v>5.529983536689542e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0006654374301433563</v>
+        <v>2.812749517033808e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0007393492851406336</v>
+        <v>9.849140951700974e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.006170616950839758</v>
+        <v>1.05199906101916e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.005741504486650229</v>
+        <v>4.827024531550705e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.006608095020055771</v>
+        <v>1.201895247504581e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.004316294565796852</v>
+        <v>5.665104981744662e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.004991922061890364</v>
+        <v>2.059482903860044e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.003217054530978203</v>
+        <v>4.931196963298135e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.003479782957583666</v>
+        <v>6.545309588545933e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.01058617047965527</v>
+        <v>9.214061719831079e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.007549950387328863</v>
+        <v>4.03182548325276e-06</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.01321285218000412</v>
+        <v>2.366210082982434e-06</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.005225914064794779</v>
+        <v>8.609658834757283e-07</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002884783316403627</v>
+        <v>6.549108366016299e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.002901303581893444</v>
+        <v>2.051578485406935e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0007162997499108315</v>
+        <v>4.739339146908605e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.004821863491088152</v>
+        <v>9.054990186996292e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.002051113173365593</v>
+        <v>2.159817267965991e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.001758971251547337</v>
+        <v>3.476068013696931e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.00147559423930943</v>
+        <v>1.853475259849802e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.005237163975834846</v>
+        <v>4.448321487870999e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.005590524058789015</v>
+        <v>1.86611468961928e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.008230580948293209</v>
+        <v>1.084879295376595e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.008563738316297531</v>
+        <v>3.927841680706479e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.002996424678713083</v>
+        <v>3.963945346185938e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.01144470367580652</v>
+        <v>1.651917955314275e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.01433752477169037</v>
+        <v>4.8369070100307e-06</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001566444989293814</v>
+        <v>2.951386704808101e-06</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.002437534043565392</v>
+        <v>4.084727152076084e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.009789523668587208</v>
+        <v>4.984936822438613e-05</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.003718142164871097</v>
+        <v>1.23242289191694e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.002743805292993784</v>
+        <v>2.883763590944e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.00186608184594661</v>
+        <v>5.048786988481879e-06</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.003308906685560942</v>
+        <v>3.04004606732633e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.006333733908832073</v>
+        <v>3.633280812209705e-06</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.00560680078342557</v>
+        <v>4.19237585447263e-06</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.005941528826951981</v>
+        <v>1.57204285642365e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.002641093218699098</v>
+        <v>2.59257503785193e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.002676256699487567</v>
+        <v>1.228442397405161e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.007337004877626896</v>
+        <v>3.132684287265874e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.008812256157398224</v>
+        <v>2.04412208404392e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0005703432252630591</v>
+        <v>2.692306225071661e-06</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.004557269625365734</v>
+        <v>6.382611900335178e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.003064330900087953</v>
+        <v>1.497486482548993e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.005006712861359119</v>
+        <v>2.306230453541502e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.003754568286240101</v>
+        <v>0.0001137720391852781</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.007686116732656956</v>
+        <v>2.526216121623293e-05</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.002206563949584961</v>
+        <v>2.491524901415687e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.01060929149389267</v>
+        <v>2.011477408814244e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.002112051704898477</v>
+        <v>2.354900061618537e-07</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0006446994957514107</v>
+        <v>4.007639290648513e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.008028661832213402</v>
+        <v>5.002434045309201e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.003808790352195501</v>
+        <v>1.360368332825601e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.002554100938141346</v>
+        <v>0.0001280221476918086</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.002251819474622607</v>
+        <v>1.477272235206328e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.01084558665752411</v>
+        <v>2.787414632621221e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.005457424558699131</v>
+        <v>8.270961188827641e-06</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.004088611342012882</v>
+        <v>6.972768460400403e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.003121792571619153</v>
+        <v>6.888392817927524e-06</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.004492179490625858</v>
+        <v>7.918955816421658e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.004604684188961983</v>
+        <v>3.7077388697071e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.01210587285459042</v>
+        <v>2.666622094693594e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0002151026856154203</v>
+        <v>2.472124651831109e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.005710121244192123</v>
+        <v>1.608482853043824e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0009210354182869196</v>
+        <v>8.964523345866837e-08</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008144271560013294</v>
+        <v>3.389544076526363e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004570763267111033</v>
+        <v>7.208801378055796e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001805705134756863</v>
+        <v>1.190809015838568e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002749538980424404</v>
+        <v>7.705423854531546e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005411015823483467</v>
+        <v>2.768333047242777e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000748204649426043</v>
+        <v>2.976940827181807e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0008939937688410282</v>
+        <v>2.282744304693551e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000262877787463367</v>
+        <v>4.337793058084571e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001025618286803365</v>
+        <v>4.171962775245674e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008066900074481964</v>
+        <v>3.189027211192297e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000179141090484336</v>
+        <v>1.231890109920641e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.372149563394487e-05</v>
+        <v>2.183770533292773e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0009598917094990611</v>
+        <v>1.347443969734741e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003756266552954912</v>
+        <v>3.559007950570958e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005736536113545299</v>
+        <v>4.524160246432984e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000433136650826782</v>
+        <v>1.188520570849505e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001154608675278723</v>
+        <v>1.768518664846397e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002040743711404502</v>
+        <v>2.369548557368262e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008132486836984754</v>
+        <v>2.135744203712875e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0006713622715324163</v>
+        <v>6.717922218513195e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002033461787505075</v>
+        <v>4.759101557283429e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003338832757435739</v>
+        <v>5.395404656383107e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002463283308316022</v>
+        <v>7.119750478068454e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0008061698172241449</v>
+        <v>1.339370072628299e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001159945852123201</v>
+        <v>8.90611460135915e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001104323426261544</v>
+        <v>5.455425977629602e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003901902236975729</v>
+        <v>1.084768257442192e-07</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0008085765293799341</v>
+        <v>8.437449849907352e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004481207579374313</v>
+        <v>6.62671340023735e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.000790164340287447</v>
+        <v>1.558453561756323e-07</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001347741927020252</v>
+        <v>9.711284576496837e-08</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0006581292254850268</v>
+        <v>1.531962254830432e-07</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0003347487945575267</v>
+        <v>2.73765010661009e-10</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001643403549678624</v>
+        <v>1.640246267697876e-07</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001485258544562384</v>
+        <v>1.677731376048541e-08</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.002249659039080143</v>
+        <v>1.941567262520039e-08</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0007096671615727246</v>
+        <v>7.850559313737904e-08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0003572350833564997</v>
+        <v>2.707976065607909e-08</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0003214317257516086</v>
+        <v>6.166634136661742e-08</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0007308619096875191</v>
+        <v>1.904317414869183e-08</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.000534597085788846</v>
+        <v>4.824830668326285e-08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0001833552232710645</v>
+        <v>8.327049982881363e-08</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0009740923997014761</v>
+        <v>1.284496420339565e-08</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.704341725097038e-05</v>
+        <v>4.13315888181387e-08</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0003981432237196714</v>
+        <v>2.84188192978263e-08</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.005083091091364622</v>
+        <v>3.053839634503674e-07</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.001013159519061446</v>
+        <v>9.058508965154033e-08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001951833837665617</v>
+        <v>3.387010494293463e-08</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0005958880065008998</v>
+        <v>1.946910828110049e-07</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.00367978191934526</v>
+        <v>2.44629859480483e-07</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.001180892111733556</v>
+        <v>4.850178214610423e-08</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.001053601736202836</v>
+        <v>5.989330276179317e-08</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0002627726644277573</v>
+        <v>1.528357707059058e-08</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005465745343826711</v>
+        <v>1.280664818636978e-08</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.002520151436328888</v>
+        <v>5.097403033005321e-08</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.001265445374883711</v>
+        <v>5.351977350187553e-08</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.000837818079162389</v>
+        <v>1.014185571079906e-07</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.002443644450977445</v>
+        <v>7.56167395365992e-08</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0009018752607516944</v>
+        <v>1.53698209715003e-08</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0006459861760959029</v>
+        <v>2.21466240901691e-08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0001607284648343921</v>
+        <v>7.495398079981896e-08</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.000745236175134778</v>
+        <v>9.777219389661695e-08</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0009842657018452883</v>
+        <v>1.270612859372022e-08</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.002165340352803469</v>
+        <v>2.654099340304583e-08</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0001064998941728845</v>
+        <v>4.229589478654816e-08</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0003427854389883578</v>
+        <v>3.611250321000625e-08</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.001377993263304234</v>
+        <v>8.920771676912409e-08</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0004168306768406183</v>
+        <v>4.524675745187778e-08</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0006510951789095998</v>
+        <v>1.87719102484607e-08</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0004693792725447565</v>
+        <v>1.059682119830541e-09</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0004378045559860766</v>
+        <v>8.85857573962312e-08</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0003323324781376868</v>
+        <v>1.169611074658405e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.002482744865119457</v>
+        <v>1.884814651020861e-07</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0001421968918293715</v>
+        <v>2.478161320595973e-08</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0001446295063942671</v>
+        <v>3.166562123624317e-08</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0004072478041052818</v>
+        <v>2.20927027783091e-08</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001264384132809937</v>
+        <v>1.533618387838942e-07</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0003775603254325688</v>
+        <v>7.332268125992414e-08</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0005753366858698428</v>
+        <v>2.943633958807368e-08</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001485486864112318</v>
+        <v>1.076428723933986e-08</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0003540839825291187</v>
+        <v>1.306593322425442e-08</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001167292008176446</v>
+        <v>1.08326943859538e-07</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0001967920397873968</v>
+        <v>1.514751879483356e-08</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0001279547868762165</v>
+        <v>3.50266127213672e-08</v>
       </c>
       <c r="CH5" t="n">
-        <v>3.012424713233486e-05</v>
+        <v>2.461843706669242e-08</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0008558568079024553</v>
+        <v>7.40379562103044e-08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002702312194742262</v>
+        <v>2.0707464187808e-08</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0003981684858445078</v>
+        <v>7.384660105635987e-10</v>
       </c>
       <c r="CL5" t="n">
-        <v>7.701246431679465e-06</v>
+        <v>4.584062196499872e-08</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.00255183270201087</v>
+        <v>5.247941459174399e-08</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0006715792696923018</v>
+        <v>1.378352294523211e-07</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0002910135372076184</v>
+        <v>1.067146797595342e-07</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001183249056339264</v>
+        <v>4.68585348301076e-08</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0006566887022927403</v>
+        <v>3.143756543977361e-08</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001080619636923075</v>
+        <v>5.269703251542524e-08</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0009802135173231363</v>
+        <v>5.93469877685493e-08</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0006449413485825062</v>
+        <v>9.503108522324055e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0004991037421859801</v>
+        <v>9.788903021501483e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0003363955183885992</v>
+        <v>9.997989103283089e-09</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.00104645814280957</v>
+        <v>9.829876290723405e-08</v>
       </c>
       <c r="CX5" t="n">
-        <v>6.914287223480642e-05</v>
+        <v>2.483071881442811e-08</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0002469049941282719</v>
+        <v>4.563590749739888e-08</v>
       </c>
       <c r="CZ5" t="n">
-        <v>6.049539661034942e-05</v>
+        <v>4.735477432404878e-08</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0008570859208703041</v>
+        <v>8.818504682039929e-08</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0002546593605075032</v>
+        <v>3.713935825544468e-08</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004507899866439402</v>
+        <v>1.050520026524282e-08</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0001930571452248842</v>
+        <v>3.998847475372713e-08</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.001632809988223016</v>
+        <v>4.988122981330889e-08</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0004715061804745346</v>
+        <v>8.071679502563711e-08</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0002600600419100374</v>
+        <v>3.505944690118667e-08</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.001501569524407387</v>
+        <v>4.447588608513797e-08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0002021308027906343</v>
+        <v>6.51153726494158e-08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001373633043840528</v>
+        <v>9.234815934178187e-08</v>
       </c>
       <c r="DK5" t="n">
-        <v>9.743234841153026e-08</v>
+        <v>1.530180426811967e-08</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.001259628916159272</v>
+        <v>9.38854753940177e-08</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.001335187582299113</v>
+        <v>7.62929186493011e-09</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0001359440211672336</v>
+        <v>6.37711794482243e-09</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003839803393930197</v>
+        <v>2.560861034339723e-08</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.000814535073004663</v>
+        <v>7.779198618607097e-09</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.002663666848093271</v>
+        <v>3.139085436032474e-08</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001313087297603488</v>
+        <v>2.262486731297031e-08</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0001725225592963398</v>
+        <v>1.273379712785072e-08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.000198229230591096</v>
+        <v>9.011660750957162e-08</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0002566143521107733</v>
+        <v>5.635929056779787e-08</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0005171812372282147</v>
+        <v>4.18662509105161e-08</v>
       </c>
       <c r="DW5" t="n">
-        <v>5.310487176757306e-05</v>
+        <v>2.127698550680179e-08</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0008582576410844922</v>
+        <v>9.877270201741339e-08</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0001161369727924466</v>
+        <v>7.591465589484869e-08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002302869543200359</v>
+        <v>8.305131871111371e-08</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001233509392477572</v>
+        <v>3.621390476382658e-08</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001151537406258285</v>
+        <v>5.722370843841418e-08</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0002488994505256414</v>
+        <v>3.647692992103657e-08</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0002889263560064137</v>
+        <v>9.406360845787276e-08</v>
       </c>
       <c r="EE5" t="n">
-        <v>2.842633693944663e-05</v>
+        <v>5.953875970021727e-08</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.001264697406440973</v>
+        <v>1.89657392013487e-08</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001658338005654514</v>
+        <v>2.752996408617037e-08</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0001882962824311107</v>
+        <v>1.560002260703186e-08</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0005739914486184716</v>
+        <v>7.761560283370272e-10</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0001690010394668207</v>
+        <v>4.707951362092899e-08</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0005958735710009933</v>
+        <v>1.152855588770763e-08</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0003061549505218863</v>
+        <v>3.123194858289935e-08</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0004501124785747379</v>
+        <v>2.318476610696507e-08</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.000346723390975967</v>
+        <v>1.920897219065409e-08</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.000355868338374421</v>
+        <v>2.959968981031125e-08</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0002928676549345255</v>
+        <v>5.79215608809136e-08</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001050450140610337</v>
+        <v>1.243478742196658e-08</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0003884902398567647</v>
+        <v>6.192179657915631e-09</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0003277328796684742</v>
+        <v>1.355454859464089e-08</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0003662628878373653</v>
+        <v>6.105027949843134e-08</v>
       </c>
       <c r="EU5" t="n">
-        <v>7.843135972507298e-05</v>
+        <v>4.279060661360745e-08</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.002778070047497749</v>
+        <v>6.019311626914714e-08</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001256402698345482</v>
+        <v>4.271782927389722e-10</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0005436738720163703</v>
+        <v>1.804563787288771e-08</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0009900646982714534</v>
+        <v>1.091176642376013e-07</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002444629790261388</v>
+        <v>1.227298973560664e-08</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0002059210673905909</v>
+        <v>4.505645279095916e-08</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0004942386294715106</v>
+        <v>9.972763059806766e-09</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0008627443457953632</v>
+        <v>6.832487997598946e-08</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001135513448389247</v>
+        <v>1.86545001668037e-08</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001590434549143538</v>
+        <v>7.76737341112721e-09</v>
       </c>
       <c r="FF5" t="n">
-        <v>8.92682874109596e-05</v>
+        <v>1.941824834261752e-08</v>
       </c>
       <c r="FG5" t="n">
-        <v>8.33957819850184e-05</v>
+        <v>1.240603708652088e-08</v>
       </c>
       <c r="FH5" t="n">
-        <v>9.885837062029168e-05</v>
+        <v>3.681625315721249e-08</v>
       </c>
       <c r="FI5" t="n">
-        <v>4.790886305272579e-05</v>
+        <v>4.421047350433582e-08</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.002238084562122822</v>
+        <v>1.968555451981047e-08</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0005126415635459125</v>
+        <v>1.894352408271516e-08</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0008931225165724754</v>
+        <v>1.134350924303362e-07</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0006780716357752681</v>
+        <v>1.300404939286182e-08</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0008817151538096368</v>
+        <v>7.395114209884923e-08</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.001317694899626076</v>
+        <v>1.333173145212641e-07</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001853187219239771</v>
+        <v>3.611677001913449e-08</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0007039314950816333</v>
+        <v>5.08958208911281e-08</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001124956761486828</v>
+        <v>7.793482836859766e-08</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0005584921455010772</v>
+        <v>3.548140270481781e-08</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001303266966715455</v>
+        <v>2.249481667604414e-08</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001111521618440747</v>
+        <v>1.418826833798903e-08</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0001459035993320867</v>
+        <v>4.882438275899403e-08</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0009338118834421039</v>
+        <v>1.932281890049126e-08</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0005038903909735382</v>
+        <v>3.785625324326247e-08</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.001432651886716485</v>
+        <v>2.502523521741296e-08</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001031813328154385</v>
+        <v>4.824924459967406e-08</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0003561936318874359</v>
+        <v>8.455968725229468e-08</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.000401912082452327</v>
+        <v>1.983940123295724e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0005214640405029058</v>
+        <v>1.34343821400762e-07</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0004423074133228511</v>
+        <v>1.12465485813118e-07</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.000208672572625801</v>
+        <v>9.527592226277193e-08</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0001535575138404965</v>
+        <v>4.646082629733428e-08</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0002089977060677484</v>
+        <v>7.329588047610969e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3.486855462142557e-07</v>
+        <v>7.622990239042338e-09</v>
       </c>
       <c r="B6" t="n">
-        <v>3.37102210323792e-06</v>
+        <v>4.34086686595947e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.383126679385896e-07</v>
+        <v>2.873870030839498e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.800467316570575e-06</v>
+        <v>2.675679944275089e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.096239770959073e-06</v>
+        <v>1.088025314288643e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.305999361051363e-07</v>
+        <v>2.777496277417413e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.425886750894279e-07</v>
+        <v>8.464935419283393e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>8.040737498049566e-08</v>
+        <v>1.212655931226436e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.168558156905419e-07</v>
+        <v>4.165592315530375e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>7.129963250918081e-07</v>
+        <v>2.566828416483702e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>2.699019432839123e-06</v>
+        <v>4.196547109813764e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.536121203571383e-07</v>
+        <v>6.762255644332527e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.395177719132334e-06</v>
+        <v>4.315975132840322e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07572088836605e-06</v>
+        <v>2.658659425947008e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.098164943869051e-06</v>
+        <v>2.674938848201691e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.860170980056864e-07</v>
+        <v>4.273351450478913e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.966700769022282e-07</v>
+        <v>6.279659903185575e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.508006306494281e-07</v>
+        <v>5.301561412096589e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>2.21860148030828e-08</v>
+        <v>1.859037701557043e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>5.085520342618111e-07</v>
+        <v>5.42124567459723e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>9.131099432124756e-08</v>
+        <v>1.102162983102062e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.471902007528115e-07</v>
+        <v>2.205927440712685e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>3.844947968900669e-07</v>
+        <v>6.802561181018518e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>3.120880194273923e-07</v>
+        <v>7.256775624853162e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.479652773170528e-07</v>
+        <v>1.190695098074457e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.526058662828291e-07</v>
+        <v>7.202507923409485e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.954508542847179e-07</v>
+        <v>3.745893817352908e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.725950085074146e-07</v>
+        <v>3.730699749127098e-09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.068702684709933e-07</v>
+        <v>7.620571729205494e-09</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.889001310928506e-08</v>
+        <v>1.503097646349261e-09</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.177216771315216e-07</v>
+        <v>1.047255704378358e-08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.269910399059881e-07</v>
+        <v>5.774101641264906e-09</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.913726149245122e-08</v>
+        <v>1.573089924988835e-08</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.1249062588995e-08</v>
+        <v>2.608744553711517e-09</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.282912571961788e-08</v>
+        <v>1.496614920881711e-08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.075143860722164e-08</v>
+        <v>1.895213541658336e-09</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.628021545409865e-07</v>
+        <v>3.506537948894106e-09</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.394475302480714e-07</v>
+        <v>8.7997182873778e-09</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.15759902996615e-07</v>
+        <v>1.256827975026908e-08</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.024411204753051e-07</v>
+        <v>9.903440734149171e-09</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.562897580242861e-07</v>
+        <v>3.90390031412835e-09</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.115988451123485e-07</v>
+        <v>4.526158559059468e-09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.966137688214076e-07</v>
+        <v>3.022024186449812e-09</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.323638088024381e-09</v>
+        <v>7.323437412054545e-10</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.446553253321326e-07</v>
+        <v>4.013829268956215e-09</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.039165908878203e-08</v>
+        <v>1.220981538097021e-09</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.097658125421731e-06</v>
+        <v>2.956311107027432e-08</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.382808250127709e-07</v>
+        <v>1.911674907262295e-08</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.123452015392104e-07</v>
+        <v>8.349654301298415e-11</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.978816754899526e-07</v>
+        <v>3.747460652903101e-08</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.552070472143896e-08</v>
+        <v>2.283236533173749e-08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.146400236962108e-07</v>
+        <v>1.947961791870512e-09</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.039211833311128e-07</v>
+        <v>4.422819444016568e-09</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.985597973292897e-07</v>
+        <v>1.526578863320083e-09</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.678528403521341e-07</v>
+        <v>2.722862824100503e-09</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.650500725096208e-07</v>
+        <v>1.472316668582607e-08</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.041157795763866e-07</v>
+        <v>1.382697512042341e-09</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.785530336448574e-07</v>
+        <v>1.028201346287005e-08</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.288938258578128e-07</v>
+        <v>2.54728718118713e-08</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.640301654035284e-07</v>
+        <v>2.159173284610461e-09</v>
       </c>
       <c r="BI6" t="n">
-        <v>7.66524976825167e-08</v>
+        <v>2.153273781502207e-09</v>
       </c>
       <c r="BJ6" t="n">
-        <v>4.841481882067455e-07</v>
+        <v>1.283816253305758e-08</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.790380359054325e-08</v>
+        <v>2.968508550083016e-09</v>
       </c>
       <c r="BL6" t="n">
-        <v>3.410564488603995e-07</v>
+        <v>2.698921086619066e-10</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.737390438298462e-07</v>
+        <v>6.452510969978675e-09</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.043017156618589e-07</v>
+        <v>5.512919010186579e-10</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.601579396355191e-09</v>
+        <v>8.147354790821737e-09</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.665173042259994e-07</v>
+        <v>1.352398015797007e-08</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.267776153530576e-07</v>
+        <v>8.935349127270342e-10</v>
       </c>
       <c r="BR6" t="n">
-        <v>8.586445687797095e-08</v>
+        <v>3.81457088138859e-09</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.256426855889003e-07</v>
+        <v>4.593839530997457e-09</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.424093909463409e-07</v>
+        <v>1.917372705051434e-09</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.523650183798964e-08</v>
+        <v>3.317933705559994e-10</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.077312845154665e-06</v>
+        <v>1.301810037546147e-08</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.273441843200999e-07</v>
+        <v>1.059578735862488e-08</v>
       </c>
       <c r="BX6" t="n">
-        <v>2.092671422815329e-07</v>
+        <v>5.060167396209181e-09</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.02492840881041e-08</v>
+        <v>4.79292516786245e-09</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.834625464880446e-07</v>
+        <v>1.156143358826967e-08</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.973126242977742e-07</v>
+        <v>1.106052138766245e-08</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.790385688124843e-08</v>
+        <v>1.31298716343764e-09</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.428860170766711e-07</v>
+        <v>6.149671882837993e-10</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.363624235750649e-08</v>
+        <v>8.113159588596375e-10</v>
       </c>
       <c r="CE6" t="n">
-        <v>5.860130727342039e-07</v>
+        <v>1.344278821591161e-08</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.94285371182923e-07</v>
+        <v>7.226549914030045e-11</v>
       </c>
       <c r="CG6" t="n">
-        <v>1.35297867132067e-07</v>
+        <v>7.801331136647605e-09</v>
       </c>
       <c r="CH6" t="n">
-        <v>7.956799663588754e-08</v>
+        <v>4.458129421180956e-09</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.256850422099888e-07</v>
+        <v>6.667787211256382e-09</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.995044840441551e-08</v>
+        <v>2.626159734120392e-09</v>
       </c>
       <c r="CK6" t="n">
-        <v>2.573024104890465e-08</v>
+        <v>1.608400967967327e-09</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.527613958136499e-07</v>
+        <v>3.614683441455213e-09</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.544433866409236e-07</v>
+        <v>1.352896372708301e-08</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.749220501778836e-07</v>
+        <v>1.935527471630394e-08</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.20833135497378e-07</v>
+        <v>1.906273539020731e-08</v>
       </c>
       <c r="CP6" t="n">
-        <v>5.718293891732174e-07</v>
+        <v>7.463892615078294e-09</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.444723001346574e-07</v>
+        <v>7.734515250490404e-09</v>
       </c>
       <c r="CR6" t="n">
-        <v>2.159149801173044e-07</v>
+        <v>3.954936822481159e-09</v>
       </c>
       <c r="CS6" t="n">
-        <v>4.390540766507911e-07</v>
+        <v>9.528325684016181e-09</v>
       </c>
       <c r="CT6" t="n">
-        <v>1.282749479969425e-07</v>
+        <v>6.240337135920981e-09</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.846686643602879e-07</v>
+        <v>1.668156279777122e-09</v>
       </c>
       <c r="CV6" t="n">
-        <v>5.130078584159037e-09</v>
+        <v>1.462198473412002e-09</v>
       </c>
       <c r="CW6" t="n">
-        <v>5.343172801985929e-07</v>
+        <v>1.237826285915844e-08</v>
       </c>
       <c r="CX6" t="n">
-        <v>3.297443527117139e-07</v>
+        <v>9.062187666941668e-10</v>
       </c>
       <c r="CY6" t="n">
-        <v>3.031107382867049e-07</v>
+        <v>8.980683752213281e-09</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.080700826605607e-07</v>
+        <v>6.4492389206805e-09</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.755866717052413e-07</v>
+        <v>7.304571614241695e-09</v>
       </c>
       <c r="DB6" t="n">
-        <v>6.015053344299304e-08</v>
+        <v>3.415426386155218e-09</v>
       </c>
       <c r="DC6" t="n">
-        <v>8.536501638900518e-08</v>
+        <v>2.276328014971796e-09</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.703522798379709e-07</v>
+        <v>3.319804209311883e-09</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.410640433936351e-07</v>
+        <v>7.960757386626938e-09</v>
       </c>
       <c r="DF6" t="n">
-        <v>4.225463499096804e-07</v>
+        <v>1.115303627230446e-09</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.939833052550966e-07</v>
+        <v>5.708736150467075e-09</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.136462856266007e-06</v>
+        <v>9.901438779991167e-09</v>
       </c>
       <c r="DI6" t="n">
-        <v>2.80054308632316e-07</v>
+        <v>3.728257258472922e-09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.138136494522769e-07</v>
+        <v>1.623354073387873e-08</v>
       </c>
       <c r="DK6" t="n">
-        <v>2.009986985740397e-07</v>
+        <v>5.630588773009038e-10</v>
       </c>
       <c r="DL6" t="n">
-        <v>1.046619928501968e-07</v>
+        <v>1.4159809325065e-08</v>
       </c>
       <c r="DM6" t="n">
-        <v>2.036426707263672e-07</v>
+        <v>7.350846598086491e-09</v>
       </c>
       <c r="DN6" t="n">
-        <v>5.577982165050344e-08</v>
+        <v>1.263070759094376e-09</v>
       </c>
       <c r="DO6" t="n">
-        <v>4.050960455970198e-07</v>
+        <v>9.056631000703419e-09</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.33250651401795e-07</v>
+        <v>8.51249626343531e-10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.527248230104306e-07</v>
+        <v>9.56478896085855e-10</v>
       </c>
       <c r="DR6" t="n">
-        <v>4.585242407983969e-08</v>
+        <v>2.506568952398425e-09</v>
       </c>
       <c r="DS6" t="n">
-        <v>2.751450622895391e-09</v>
+        <v>3.925690883477273e-09</v>
       </c>
       <c r="DT6" t="n">
-        <v>1.724729514762657e-07</v>
+        <v>7.963639525598865e-09</v>
       </c>
       <c r="DU6" t="n">
-        <v>5.356073984330578e-08</v>
+        <v>8.651723781838427e-09</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.168753721638495e-07</v>
+        <v>1.612639577430741e-09</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.411449600003834e-07</v>
+        <v>8.308310706084399e-10</v>
       </c>
       <c r="DX6" t="n">
-        <v>2.02566681650751e-07</v>
+        <v>5.066346009385825e-09</v>
       </c>
       <c r="DY6" t="n">
-        <v>4.319010429298942e-07</v>
+        <v>1.091362467064982e-08</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.980674824153539e-08</v>
+        <v>9.069819562057546e-09</v>
       </c>
       <c r="EA6" t="n">
-        <v>4.372738970914725e-08</v>
+        <v>5.954189141732513e-09</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.753650025193565e-07</v>
+        <v>9.011820623072708e-09</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.220195713358407e-07</v>
+        <v>2.180401414975108e-09</v>
       </c>
       <c r="ED6" t="n">
-        <v>3.498376699440087e-09</v>
+        <v>1.311132891146372e-08</v>
       </c>
       <c r="EE6" t="n">
-        <v>7.316133121548773e-08</v>
+        <v>3.401628534405177e-09</v>
       </c>
       <c r="EF6" t="n">
-        <v>1.55804855239694e-07</v>
+        <v>2.551445277276798e-09</v>
       </c>
       <c r="EG6" t="n">
-        <v>4.725147562112397e-07</v>
+        <v>3.265534509466761e-09</v>
       </c>
       <c r="EH6" t="n">
-        <v>2.881625391637499e-07</v>
+        <v>5.286200366327876e-09</v>
       </c>
       <c r="EI6" t="n">
-        <v>9.793629374144075e-08</v>
+        <v>5.60369617375045e-09</v>
       </c>
       <c r="EJ6" t="n">
-        <v>2.095224687082009e-07</v>
+        <v>6.233616289819111e-09</v>
       </c>
       <c r="EK6" t="n">
-        <v>2.010115167649928e-07</v>
+        <v>6.187306667015946e-09</v>
       </c>
       <c r="EL6" t="n">
-        <v>1.011128958339214e-07</v>
+        <v>3.990300090350729e-09</v>
       </c>
       <c r="EM6" t="n">
-        <v>2.506380702982369e-08</v>
+        <v>1.080882050530363e-09</v>
       </c>
       <c r="EN6" t="n">
-        <v>9.857676985802755e-08</v>
+        <v>1.285288542263174e-09</v>
       </c>
       <c r="EO6" t="n">
-        <v>8.832962805627176e-08</v>
+        <v>1.045740605221113e-09</v>
       </c>
       <c r="EP6" t="n">
-        <v>2.42328411559356e-07</v>
+        <v>5.947674797113223e-09</v>
       </c>
       <c r="EQ6" t="n">
-        <v>4.556753765427857e-07</v>
+        <v>3.71241881680362e-09</v>
       </c>
       <c r="ER6" t="n">
-        <v>1.41860553526385e-07</v>
+        <v>4.562488165049672e-09</v>
       </c>
       <c r="ES6" t="n">
-        <v>2.116461104151313e-07</v>
+        <v>3.406795734406387e-09</v>
       </c>
       <c r="ET6" t="n">
-        <v>3.188073094406718e-08</v>
+        <v>1.128565463304199e-09</v>
       </c>
       <c r="EU6" t="n">
-        <v>9.818015200835362e-08</v>
+        <v>1.998908594202931e-09</v>
       </c>
       <c r="EV6" t="n">
-        <v>4.733468870199431e-07</v>
+        <v>7.693493841998134e-09</v>
       </c>
       <c r="EW6" t="n">
-        <v>2.250197539410692e-08</v>
+        <v>7.159658643729472e-09</v>
       </c>
       <c r="EX6" t="n">
-        <v>6.028346888342639e-08</v>
+        <v>8.224373404530638e-10</v>
       </c>
       <c r="EY6" t="n">
-        <v>5.324162088982121e-07</v>
+        <v>1.412172334624984e-08</v>
       </c>
       <c r="EZ6" t="n">
-        <v>2.669382297426637e-07</v>
+        <v>8.283674857167966e-10</v>
       </c>
       <c r="FA6" t="n">
-        <v>1.823477759899106e-07</v>
+        <v>9.598315031666971e-09</v>
       </c>
       <c r="FB6" t="n">
-        <v>9.769066622311584e-08</v>
+        <v>2.358808259828038e-09</v>
       </c>
       <c r="FC6" t="n">
-        <v>2.471676054938143e-07</v>
+        <v>5.670834912763212e-09</v>
       </c>
       <c r="FD6" t="n">
-        <v>8.326153988491569e-08</v>
+        <v>1.230767043836067e-09</v>
       </c>
       <c r="FE6" t="n">
-        <v>3.003509618793032e-08</v>
+        <v>3.465477682595974e-09</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.684807896002894e-07</v>
+        <v>8.044525601214048e-10</v>
       </c>
       <c r="FG6" t="n">
-        <v>2.948289363757794e-07</v>
+        <v>1.944781002904961e-09</v>
       </c>
       <c r="FH6" t="n">
-        <v>2.964027245866419e-08</v>
+        <v>6.508666050564216e-09</v>
       </c>
       <c r="FI6" t="n">
-        <v>4.243798628067452e-07</v>
+        <v>6.620942016866138e-09</v>
       </c>
       <c r="FJ6" t="n">
-        <v>3.620421864525269e-07</v>
+        <v>6.443571898273603e-09</v>
       </c>
       <c r="FK6" t="n">
-        <v>1.579079444979925e-08</v>
+        <v>1.298633089952261e-09</v>
       </c>
       <c r="FL6" t="n">
-        <v>3.563259838301747e-07</v>
+        <v>1.8896348930042e-09</v>
       </c>
       <c r="FM6" t="n">
-        <v>2.701854384667968e-08</v>
+        <v>1.046408792948483e-10</v>
       </c>
       <c r="FN6" t="n">
-        <v>4.110903830678581e-07</v>
+        <v>4.738029968365254e-10</v>
       </c>
       <c r="FO6" t="n">
-        <v>1.647045877462006e-07</v>
+        <v>1.001083393958879e-08</v>
       </c>
       <c r="FP6" t="n">
-        <v>1.101380320278622e-07</v>
+        <v>6.398905849636094e-09</v>
       </c>
       <c r="FQ6" t="n">
-        <v>1.515033147825307e-07</v>
+        <v>1.479476363641652e-08</v>
       </c>
       <c r="FR6" t="n">
-        <v>1.864830068143419e-07</v>
+        <v>1.403923288734177e-08</v>
       </c>
       <c r="FS6" t="n">
-        <v>1.949380532551004e-07</v>
+        <v>5.043536255300296e-09</v>
       </c>
       <c r="FT6" t="n">
-        <v>4.180322150659777e-07</v>
+        <v>1.902086843585948e-08</v>
       </c>
       <c r="FU6" t="n">
-        <v>2.339749016755377e-07</v>
+        <v>3.541518855953996e-09</v>
       </c>
       <c r="FV6" t="n">
-        <v>2.668860688004315e-08</v>
+        <v>1.127761439789765e-08</v>
       </c>
       <c r="FW6" t="n">
-        <v>2.886663139634038e-07</v>
+        <v>4.779230344809093e-09</v>
       </c>
       <c r="FX6" t="n">
-        <v>2.961237157705909e-07</v>
+        <v>4.585875235108006e-09</v>
       </c>
       <c r="FY6" t="n">
-        <v>6.741734068782534e-07</v>
+        <v>9.998478711636949e-10</v>
       </c>
       <c r="FZ6" t="n">
-        <v>1.04438242942706e-07</v>
+        <v>2.940727661382425e-10</v>
       </c>
       <c r="GA6" t="n">
-        <v>1.516102088316984e-07</v>
+        <v>1.13226654718801e-08</v>
       </c>
       <c r="GB6" t="n">
-        <v>7.387743750086884e-08</v>
+        <v>6.963317478181352e-09</v>
       </c>
       <c r="GC6" t="n">
-        <v>2.936281475740543e-07</v>
+        <v>1.223960488516695e-08</v>
       </c>
       <c r="GD6" t="n">
-        <v>2.773087715013389e-07</v>
+        <v>1.756561474053342e-08</v>
       </c>
       <c r="GE6" t="n">
-        <v>7.562042014797044e-07</v>
+        <v>1.217743061943111e-08</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.701233571793637e-07</v>
+        <v>4.73887151741792e-10</v>
       </c>
       <c r="GG6" t="n">
-        <v>2.910508953846147e-07</v>
+        <v>3.37366523606164e-10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0002374263131059706</v>
+        <v>3.536713484209031e-05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002523765899240971</v>
+        <v>8.004491974133998e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003460117732174695</v>
+        <v>0.0001535841001896188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002188677899539471</v>
+        <v>8.259585592895746e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0006042835884727538</v>
+        <v>0.0003356907109264284</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004816655535250902</v>
+        <v>0.0006798270624130964</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001463473308831453</v>
+        <v>0.0001741002197377384</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003200932405889034</v>
+        <v>0.0003661515365820378</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0006251570302993059</v>
+        <v>5.967128527117893e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003996531304437667</v>
+        <v>5.735081867896952e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002777280518785119</v>
+        <v>0.0001949799043359235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000243763264734298</v>
+        <v>0.0002673450508154929</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007626391598023474</v>
+        <v>0.0001009530751616694</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001703612972050905</v>
+        <v>0.0004315541591495275</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004250139929354191</v>
+        <v>0.0008789892890490592</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002046583220362663</v>
+        <v>0.0002961776335723698</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000573975732550025</v>
+        <v>0.0004860341432504356</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001351870014332235</v>
+        <v>0.0002380883379373699</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001588760642334819</v>
+        <v>4.317770799389109e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0005583931342698634</v>
+        <v>4.084821193828247e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0005288562970235944</v>
+        <v>8.972250361694023e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0005930119077675045</v>
+        <v>1.594479908817448e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001058021909557283</v>
+        <v>1.464704200770939e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0006622343207709491</v>
+        <v>0.0001026735990308225</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.553639054298401e-05</v>
+        <v>7.31328982510604e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000158166978508234</v>
+        <v>4.661109778680839e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002394411567365751</v>
+        <v>1.825333310989663e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0008470246102660894</v>
+        <v>2.438157025608234e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.000124843863886781</v>
+        <v>7.775596168357879e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001788462104741484</v>
+        <v>3.61161983164493e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0001769242517184466</v>
+        <v>7.253344665514305e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0003467600618023425</v>
+        <v>7.274458039319143e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0006321848486550152</v>
+        <v>4.309321229811758e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0003640481154434383</v>
+        <v>7.87031021900475e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0004849391989409924</v>
+        <v>8.500400872435421e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0009250554139725864</v>
+        <v>2.692204361665063e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0006574410945177078</v>
+        <v>0.0001002637000055984</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0004799373564310372</v>
+        <v>2.103913720929995e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0004169661551713943</v>
+        <v>2.685111394384876e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.041412077844143e-05</v>
+        <v>8.017949585337192e-05</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0006322961417026818</v>
+        <v>7.191600275291421e-07</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001254020258784294</v>
+        <v>9.94370348053053e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.419774970505387e-05</v>
+        <v>8.023760528885759e-06</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0009345617727376521</v>
+        <v>7.516691766795702e-06</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.382798993494362e-05</v>
+        <v>1.271848850592505e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.00133896095212549</v>
+        <v>0.0001648286415729672</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.001851633074693382</v>
+        <v>0.0004914276651106775</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0005236744182184339</v>
+        <v>4.714621900347993e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0005071128834970295</v>
+        <v>0.0001660771522438154</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0009627314284443855</v>
+        <v>5.472098200698383e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0008339757332578301</v>
+        <v>0.0005048660677857697</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0004255651438143104</v>
+        <v>0.0001200150509248488</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.002254186663776636</v>
+        <v>0.0002228279045084491</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0005258105229586363</v>
+        <v>4.073017771588638e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001176719088107347</v>
+        <v>0.0001785686472430825</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.314834460383281e-05</v>
+        <v>0.0002262309426441789</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0004109768487978727</v>
+        <v>8.140466525219381e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.000911257229745388</v>
+        <v>0.0002412859757896513</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0007379283779300749</v>
+        <v>0.0001291252119699493</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002582289278507233</v>
+        <v>4.225437442073599e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00106522417627275</v>
+        <v>4.333393007982522e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002275377191836014</v>
+        <v>0.000141848431667313</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0003275170456618071</v>
+        <v>2.306133137608413e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002722183999139816</v>
+        <v>6.366131856339052e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0004270153003744781</v>
+        <v>0.0002336095203645527</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0005080648115836084</v>
+        <v>0.0002192998363170773</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001000064774416387</v>
+        <v>0.0001279693678952754</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0002312996075488627</v>
+        <v>0.0001767799403751269</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0006817643297836185</v>
+        <v>0.0001098329012165777</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001373191480524838</v>
+        <v>6.481049058493227e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0002265449438709766</v>
+        <v>0.000137152019306086</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0006518752197735012</v>
+        <v>7.274840754689649e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>8.5296924225986e-06</v>
+        <v>2.764840246527456e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0008066978771239519</v>
+        <v>0.0001869990810519084</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0004031300195492804</v>
+        <v>5.393014725996181e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0002244158677058294</v>
+        <v>0.0001464225351810455</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0005352637963369489</v>
+        <v>4.493425876717083e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0003775343939196318</v>
+        <v>0.0002879155217669904</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0001672197395237163</v>
+        <v>8.057444210862741e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0007883792277425528</v>
+        <v>0.0001059191708918661</v>
       </c>
       <c r="CC7" t="n">
-        <v>8.522278949385509e-05</v>
+        <v>2.641686842252966e-05</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0001839088363340124</v>
+        <v>1.285624330193968e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0002978660340886563</v>
+        <v>9.325181963504292e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>5.064087599748746e-05</v>
+        <v>4.31358021160122e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0006833364022895694</v>
+        <v>4.639657709049061e-05</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.000147166836541146</v>
+        <v>0.0001198937170556746</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.000535413739271462</v>
+        <v>0.0001830298569984734</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.000564145331736654</v>
+        <v>6.446614133892581e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0003423955058678985</v>
+        <v>1.244331997440895e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>4.264155722921714e-05</v>
+        <v>1.615829387446865e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0004811579128727317</v>
+        <v>1.352930121356621e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0005449388409033418</v>
+        <v>9.655015310272574e-05</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0003529594978317618</v>
+        <v>3.041016680072062e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0005751105491071939</v>
+        <v>4.725948019768111e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0004386866639833897</v>
+        <v>5.079476977698505e-05</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0005922384443692863</v>
+        <v>1.940885704243556e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0005958392866887152</v>
+        <v>0.0002060307888314128</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0001157633378170431</v>
+        <v>5.633623004541732e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0006480521988123655</v>
+        <v>7.650619227206334e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>5.128400516696274e-06</v>
+        <v>2.081884122162592e-05</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0003171322168782353</v>
+        <v>5.660887836711481e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>8.643584442324936e-05</v>
+        <v>5.998661799822003e-05</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0005202259635552764</v>
+        <v>5.367157427826896e-05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>8.171143417712301e-05</v>
+        <v>0.0001547609135741368</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0007643777644261718</v>
+        <v>0.0001929941645357758</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0005306777893565595</v>
+        <v>4.137145879212767e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0004559509106911719</v>
+        <v>3.345413279021159e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0002781941439025104</v>
+        <v>1.823922139010392e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0002536923857405782</v>
+        <v>0.0001674101804383099</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.001410113763995469</v>
+        <v>0.0001728689094306901</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0003748437447939068</v>
+        <v>7.181371620390564e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.00250391848385334</v>
+        <v>7.110319711500779e-05</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.002306014765053988</v>
+        <v>5.843195322086103e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.002508270787075162</v>
+        <v>2.225046227977145e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0008905349532142282</v>
+        <v>8.026675641303882e-05</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.000589547271374613</v>
+        <v>5.151485675014555e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>2.202227915404364e-05</v>
+        <v>0.0001843033824115992</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0001258950505871326</v>
+        <v>2.482124546077102e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0003459297586232424</v>
+        <v>0.000123260062537156</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0002413007750874385</v>
+        <v>4.827315933653153e-05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0004977022181265056</v>
+        <v>4.734788672067225e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001316178473643959</v>
+        <v>9.828170004766434e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>4.982216341886669e-05</v>
+        <v>0.000134802030515857</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.002067752182483673</v>
+        <v>7.160114910220727e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0001394618884660304</v>
+        <v>6.149217369966209e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0005294250440783799</v>
+        <v>0.0001566044229548424</v>
       </c>
       <c r="DW7" t="n">
-        <v>3.171380376443267e-05</v>
+        <v>3.872344677802175e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0007866026135161519</v>
+        <v>0.000130785585497506</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0008642965694889426</v>
+        <v>0.0001030025450745597</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0001841109478846192</v>
+        <v>5.555835377890617e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001123781083151698</v>
+        <v>1.943913730428903e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0004651288036257029</v>
+        <v>4.717341653304175e-06</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0002627804933581501</v>
+        <v>3.142202695016749e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0004793237894773483</v>
+        <v>7.468306284863502e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0003271734167356044</v>
+        <v>6.607295654248446e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>5.537563993129879e-06</v>
+        <v>7.822154657333158e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0004119369550608099</v>
+        <v>1.919505848491099e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0002147125196643174</v>
+        <v>6.063091495889239e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0003417374973651022</v>
+        <v>0.0001724446337902918</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0002356767363380641</v>
+        <v>0.0001123829424614087</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001204285537824035</v>
+        <v>8.763093501329422e-05</v>
       </c>
       <c r="EL7" t="n">
-        <v>9.466413757763803e-05</v>
+        <v>7.133444887585938e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>7.515001925639808e-06</v>
+        <v>5.058827809989452e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.000338839105097577</v>
+        <v>1.166488982562441e-05</v>
       </c>
       <c r="EO7" t="n">
-        <v>7.652854401385412e-05</v>
+        <v>5.489774775924161e-05</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0003263507387600839</v>
+        <v>4.888414332526736e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0001466195972170681</v>
+        <v>1.482365587435197e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.00075849040877074</v>
+        <v>8.788793638814241e-05</v>
       </c>
       <c r="ES7" t="n">
-        <v>9.513692202745005e-05</v>
+        <v>0.0002403232647338882</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0006495980196632445</v>
+        <v>0.0001614855427760631</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0007080381619744003</v>
+        <v>0.0001270393113372847</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.000728482031263411</v>
+        <v>6.724899139953777e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0007874618750065565</v>
+        <v>2.257886808365583e-05</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001516962074674666</v>
+        <v>3.531545371515676e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0002138304407708347</v>
+        <v>7.375127097475342e-06</v>
       </c>
       <c r="EZ7" t="n">
-        <v>8.600180444773287e-05</v>
+        <v>3.295619535492733e-05</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0005733727593906224</v>
+        <v>4.29756473749876e-05</v>
       </c>
       <c r="FB7" t="n">
-        <v>4.029960837215185e-05</v>
+        <v>0.0001080694710253738</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0006617263425141573</v>
+        <v>0.000200675698579289</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0005867599393241107</v>
+        <v>8.700444595888257e-05</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0004496744659263641</v>
+        <v>1.3685039448319e-05</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0002919729449786246</v>
+        <v>7.902704965090379e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>2.328273694729432e-05</v>
+        <v>4.87598663312383e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.001262950128875673</v>
+        <v>3.312230182928033e-05</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0007431039121001959</v>
+        <v>1.592427361174487e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0008654854027554393</v>
+        <v>5.177025741431862e-05</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.000488457502797246</v>
+        <v>9.471010707784444e-05</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0002679043100215495</v>
+        <v>8.030453318497166e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0002883840352296829</v>
+        <v>3.330559411551803e-05</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0006282557733356953</v>
+        <v>8.684706699568778e-05</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0003989133110735565</v>
+        <v>0.000107356856460683</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.369020537822507e-05</v>
+        <v>3.857161937048659e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.001081103808246553</v>
+        <v>0.0002212078252341598</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001842471654526889</v>
+        <v>9.641135693527758e-05</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0002384409017395228</v>
+        <v>9.407616744283587e-05</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001955617219209671</v>
+        <v>0.0003652125305961818</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0004704095190390944</v>
+        <v>6.807248428231105e-05</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0003462505992501974</v>
+        <v>1.988055009860545e-05</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.001882411888800561</v>
+        <v>3.485186607576907e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0001665577001404017</v>
+        <v>0.0001458157785236835</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0001139307714765891</v>
+        <v>3.628025660873391e-05</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0002783000818453729</v>
+        <v>5.728390169679187e-05</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0004884188529103994</v>
+        <v>0.0001807317603379488</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0003703508118633181</v>
+        <v>2.024697096203454e-05</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.002002417808398604</v>
+        <v>9.35668867896311e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0007123156683519483</v>
+        <v>2.699888682400342e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.00113112828694284</v>
+        <v>0.0001951691374415532</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0005986580508761108</v>
+        <v>0.0001032701402436942</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0007440397748723626</v>
+        <v>2.813734226947417e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0004118129727430642</v>
+        <v>0.1085646823048592</v>
       </c>
       <c r="B8" t="n">
-        <v>0.007756754290312529</v>
+        <v>1.021109223365784</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000422396813519299</v>
+        <v>0.0380321741104126</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003180555999279022</v>
+        <v>0.2766221761703491</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007339577423408628</v>
+        <v>0.5042160749435425</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005864545237272978</v>
+        <v>0.8180153369903564</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005485326983034611</v>
+        <v>0.4130997359752655</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002456562127918005</v>
+        <v>1.146449446678162</v>
       </c>
       <c r="I8" t="n">
-        <v>4.051224823342636e-05</v>
+        <v>0.2431680858135223</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001661615213379264</v>
+        <v>0.05473300814628601</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006437366362661123</v>
+        <v>1.200941681861877</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003637332993093878</v>
+        <v>0.2245233952999115</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003352949395775795</v>
+        <v>0.5455113649368286</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0003611576976254582</v>
+        <v>1.439121603965759</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005545507650822401</v>
+        <v>0.9781197905540466</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0008413924952037632</v>
+        <v>0.2848686575889587</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008144238963723183</v>
+        <v>0.9392232298851013</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0007833329145796597</v>
+        <v>0.3916301131248474</v>
       </c>
       <c r="S8" t="n">
-        <v>5.475504076457582e-05</v>
+        <v>0.165513664484024</v>
       </c>
       <c r="T8" t="n">
-        <v>0.000650558271445334</v>
+        <v>0.2361571788787842</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0003979194443672895</v>
+        <v>0.1088635548949242</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000890272727701813</v>
+        <v>0.4232285618782043</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0009570568799972534</v>
+        <v>0.2461090981960297</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001007641316391528</v>
+        <v>0.1713123321533203</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00070143339689821</v>
+        <v>0.1142114326357841</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001104658702388406</v>
+        <v>0.1605732589960098</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001025261241011322</v>
+        <v>0.001814901828765869</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.624702993780375e-05</v>
+        <v>0.2231440842151642</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001038017449900508</v>
+        <v>0.3404627442359924</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0003369622281752527</v>
+        <v>0.04554818570613861</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0005372431478463113</v>
+        <v>0.398312121629715</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0003466648049652576</v>
+        <v>0.3626108169555664</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002582592715043575</v>
+        <v>0.2252554893493652</v>
       </c>
       <c r="AH8" t="n">
-        <v>8.894203347153962e-05</v>
+        <v>0.0117456242442131</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0001163516353699379</v>
+        <v>0.3273480236530304</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0003536911681294441</v>
+        <v>0.2078892439603806</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0007593021146021783</v>
+        <v>0.2858917713165283</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0008937341626733541</v>
+        <v>0.3595708310604095</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0001060988870449364</v>
+        <v>0.1043777242302895</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0007511891890317202</v>
+        <v>0.06629832088947296</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0007590733584947884</v>
+        <v>0.1641089767217636</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001238575205206871</v>
+        <v>0.2006572484970093</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0003379251284059137</v>
+        <v>0.1019016429781914</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0003488370857667178</v>
+        <v>0.2288595587015152</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0009130854159593582</v>
+        <v>0.06344233453273773</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0009974436834454536</v>
+        <v>0.1046040207147598</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.004815455060452223</v>
+        <v>1.94943368434906</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0006242240197025239</v>
+        <v>0.04747293144464493</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0002660881436895579</v>
+        <v>0.2424208074808121</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.000286811264231801</v>
+        <v>0.2319469898939133</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.00390477804467082</v>
+        <v>0.692006528377533</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001380173140205443</v>
+        <v>0.09056589007377625</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001135177095420659</v>
+        <v>0.3267459273338318</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0022151586599648</v>
+        <v>0.1108988374471664</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0009359559044241905</v>
+        <v>0.1551438421010971</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.001637836219742894</v>
+        <v>0.6901437640190125</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001805179635994136</v>
+        <v>0.05417690798640251</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001113621750846505</v>
+        <v>0.1597884744405746</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001551203895360231</v>
+        <v>0.3191340863704681</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001571945496834815</v>
+        <v>0.1343685388565063</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.00109085557051003</v>
+        <v>0.1235750094056129</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0009566480293869972</v>
+        <v>0.5315117239952087</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.000576210324652493</v>
+        <v>0.07758221030235291</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002434018824715167</v>
+        <v>0.06193191558122635</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001655094791203737</v>
+        <v>0.2159051299095154</v>
       </c>
       <c r="BN8" t="n">
-        <v>9.593482536729425e-05</v>
+        <v>0.3765617311000824</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0007076783804222941</v>
+        <v>0.09096748381853104</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002834241895470768</v>
+        <v>0.2167304456233978</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0005569712375290692</v>
+        <v>0.2079620957374573</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0003283550904598087</v>
+        <v>0.3243005573749542</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0002256097504869103</v>
+        <v>0.06044743210077286</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0009117294102907181</v>
+        <v>0.02010261826217175</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0004342779866419733</v>
+        <v>0.1891173124313354</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002745712641626596</v>
+        <v>0.771762490272522</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0009119783062487841</v>
+        <v>0.03736426681280136</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.000428529514465481</v>
+        <v>0.4022414982318878</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0001071296428563073</v>
+        <v>0.364467591047287</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001949265832081437</v>
+        <v>0.3395852446556091</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.259689452126622e-05</v>
+        <v>0.3224305510520935</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0005339424824342132</v>
+        <v>0.2762607038021088</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001068686367943883</v>
+        <v>0.002202675677835941</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.578006675932556e-05</v>
+        <v>0.04341666027903557</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001112511847168207</v>
+        <v>0.3388303220272064</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0007332982495427132</v>
+        <v>0.09429271519184113</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0004150521417614073</v>
+        <v>0.09824934601783752</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0001154752681031823</v>
+        <v>0.2175338268280029</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0008121521095745265</v>
+        <v>0.2301478534936905</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.000508734374307096</v>
+        <v>0.07661724835634232</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.000495127635076642</v>
+        <v>0.03777434676885605</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0006315935170277953</v>
+        <v>0.01373821124434471</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0008373979362659156</v>
+        <v>0.27439945936203</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0005343370139598846</v>
+        <v>0.3903340697288513</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0001617862144485116</v>
+        <v>0.1826540231704712</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001126809744164348</v>
+        <v>0.6690869927406311</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0001454395242035389</v>
+        <v>0.4146171510219574</v>
       </c>
       <c r="CR8" t="n">
-        <v>3.553688293322921e-05</v>
+        <v>0.1685066670179367</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0009846515022218227</v>
+        <v>0.01544108428061008</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0009280579397454858</v>
+        <v>0.1883959323167801</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001371886173728853</v>
+        <v>0.01361189410090446</v>
       </c>
       <c r="CV8" t="n">
-        <v>4.911555879516527e-05</v>
+        <v>0.1226556897163391</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0009619264164939523</v>
+        <v>0.2987266182899475</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.000802986731287092</v>
+        <v>0.1058980822563171</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0007353606633841991</v>
+        <v>0.152635931968689</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002419349475530908</v>
+        <v>0.2153743952512741</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0008427781285718083</v>
+        <v>0.301397293806076</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0004146330174989998</v>
+        <v>0.007592816837131977</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.000859975116327405</v>
+        <v>0.01255198195576668</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0005196037818677723</v>
+        <v>0.00973116047680378</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0003694098559208214</v>
+        <v>0.05121967196464539</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0006494661793112755</v>
+        <v>0.1843187510967255</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.099466655636206e-06</v>
+        <v>0.1124333888292313</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.003101311391219497</v>
+        <v>0.1714845448732376</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0001211488852277398</v>
+        <v>0.5169990062713623</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002420138800516725</v>
+        <v>0.3893471360206604</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0006956837605684996</v>
+        <v>0.1140749007463455</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001732248696498573</v>
+        <v>0.04539894312620163</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.001112361089326441</v>
+        <v>0.07905136048793793</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0001216532473335974</v>
+        <v>0.1715354770421982</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0005922499112784863</v>
+        <v>0.1657265722751617</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0003121623594779521</v>
+        <v>0.098326176404953</v>
       </c>
       <c r="DQ8" t="n">
-        <v>2.654627314768732e-05</v>
+        <v>0.08442283421754837</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001113657854148187</v>
+        <v>0.2406525462865829</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0007385864737443626</v>
+        <v>0.1745487302541733</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.000110156019218266</v>
+        <v>0.1819551587104797</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0002453447959851474</v>
+        <v>0.05007999390363693</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0006171002169139683</v>
+        <v>0.342274397611618</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001774419797584414</v>
+        <v>0.2002217173576355</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0001146161885117181</v>
+        <v>0.4021744430065155</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.00085062300786376</v>
+        <v>0.1245522871613503</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0004332169482950121</v>
+        <v>0.005681239068508148</v>
       </c>
       <c r="EA8" t="n">
-        <v>5.801381485071033e-05</v>
+        <v>0.221304327249527</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.001008750055916607</v>
+        <v>0.04809956252574921</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0001921435759868473</v>
+        <v>0.01918351277709007</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003670227015390992</v>
+        <v>0.2437146157026291</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.00110764498822391</v>
+        <v>0.3440817594528198</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.000315052893711254</v>
+        <v>0.01384299993515015</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0006094678537920117</v>
+        <v>0.243061900138855</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0005905646248720586</v>
+        <v>0.1441054940223694</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0002355063916184008</v>
+        <v>0.07424475252628326</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0004622415290214121</v>
+        <v>0.2763164639472961</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0002024084533331916</v>
+        <v>0.1660359352827072</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0007599826203659177</v>
+        <v>0.04066352546215057</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0005760305793955922</v>
+        <v>0.1444746851921082</v>
       </c>
       <c r="EN8" t="n">
-        <v>9.835670061875135e-05</v>
+        <v>0.009055683389306068</v>
       </c>
       <c r="EO8" t="n">
-        <v>4.533008905127645e-05</v>
+        <v>0.1469220221042633</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0005720889312215149</v>
+        <v>0.2221356332302094</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0009157411986961961</v>
+        <v>0.1697671413421631</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0002602490421850234</v>
+        <v>0.03646636754274368</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0005304197547957301</v>
+        <v>0.1545308232307434</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0001891443971544504</v>
+        <v>0.2529759705066681</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0008948687463998795</v>
+        <v>0.05733045190572739</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.001614282606169581</v>
+        <v>0.0476473942399025</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0003199102648068219</v>
+        <v>0.2727341055870056</v>
       </c>
       <c r="EX8" t="n">
-        <v>4.806947254110128e-05</v>
+        <v>0.09276892244815826</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.000984931131824851</v>
+        <v>0.3796289563179016</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0005924647557549179</v>
+        <v>0.06732019037008286</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0003447326307650656</v>
+        <v>0.1801110208034515</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0002935984230134636</v>
+        <v>0.1713873445987701</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0006848868215456605</v>
+        <v>0.282723605632782</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0008298109169118106</v>
+        <v>0.09903442114591599</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0005210612434893847</v>
+        <v>0.03745768964290619</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0008355280733667314</v>
+        <v>0.03659624978899956</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0005222597392275929</v>
+        <v>0.05942150950431824</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0006210406427271664</v>
+        <v>0.1393234729766846</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.000554107129573822</v>
+        <v>0.25556880235672</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.001472773728892207</v>
+        <v>0.2675189971923828</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0001247907057404518</v>
+        <v>0.02069359086453915</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0006381084676831961</v>
+        <v>0.1761154979467392</v>
       </c>
       <c r="FM8" t="n">
-        <v>8.785462705418468e-05</v>
+        <v>0.3110276758670807</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0005224636988714337</v>
+        <v>0.1338250935077667</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0005231930408626795</v>
+        <v>0.3310009837150574</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0006523008341901004</v>
+        <v>0.2161502540111542</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0003317184746265411</v>
+        <v>0.01737438142299652</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0006565037765540183</v>
+        <v>0.2100310921669006</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0008483353885821998</v>
+        <v>0.2516216039657593</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0004996851203031838</v>
+        <v>0.6156765818595886</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0005580995930358768</v>
+        <v>0.157831221818924</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0007286160252988338</v>
+        <v>0.1772186458110809</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0008091498166322708</v>
+        <v>0.451951652765274</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0008693806594237685</v>
+        <v>0.2549871504306793</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.001355200656689703</v>
+        <v>0.1494167447090149</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0002858682128135115</v>
+        <v>0.02983042597770691</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0008948341128416359</v>
+        <v>0.223090648651123</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0002462587144691497</v>
+        <v>0.1123302578926086</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0004305460897739977</v>
+        <v>0.1993634104728699</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0006741653778590262</v>
+        <v>0.04868578910827637</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.002687775762751698</v>
+        <v>0.1820282340049744</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0008148502092808485</v>
+        <v>0.1069272011518478</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0003641460789367557</v>
+        <v>0.07218153774738312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.467221203010354e-10</v>
+        <v>6.224520898712171e-09</v>
       </c>
       <c r="B9" t="n">
-        <v>5.241297396096911e-10</v>
+        <v>3.433967776800273e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.926535290827871e-10</v>
+        <v>7.369573395976659e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.327869256888107e-10</v>
+        <v>1.504720259504211e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.039029442130641e-10</v>
+        <v>7.695457604484091e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.455565667995984e-10</v>
+        <v>2.95441520137274e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.990631353672057e-11</v>
+        <v>1.010105421528351e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.499308730090192e-11</v>
+        <v>1.316363018588618e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.275905657851297e-10</v>
+        <v>1.17065546145767e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>3.170376183803114e-10</v>
+        <v>1.871360844063474e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>7.983579353165737e-10</v>
+        <v>3.444979768119083e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.979754554737312e-10</v>
+        <v>9.566345937628284e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.615542144506321e-10</v>
+        <v>1.771265445427161e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.689544476546345e-10</v>
+        <v>2.063836745946901e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.612131067003531e-10</v>
+        <v>2.98269924314809e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.892411670758378e-10</v>
+        <v>9.116267740694184e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.098526907801102e-10</v>
+        <v>7.012131320038861e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.853831810283424e-10</v>
+        <v>8.4876811135004e-10</v>
       </c>
       <c r="S9" t="n">
-        <v>1.853161929465941e-10</v>
+        <v>5.351719511992314e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>2.176717972535158e-10</v>
+        <v>1.000417748642235e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.678146233086153e-10</v>
+        <v>5.858960872018315e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>2.189023129428591e-10</v>
+        <v>6.886367920344583e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>6.321529411046356e-10</v>
+        <v>2.328655490657638e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.206410804588387e-10</v>
+        <v>1.763672430321606e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.640618917444272e-10</v>
+        <v>3.770023404570111e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.295877571916293e-10</v>
+        <v>1.74075776016025e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.954703204853914e-10</v>
+        <v>3.962989658656824e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.486393508276507e-10</v>
+        <v>4.273885245709153e-09</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.299167384256506e-10</v>
+        <v>9.276921453249543e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.61708005161654e-10</v>
+        <v>6.354112791484567e-09</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.127182236437818e-10</v>
+        <v>4.273011722233377e-09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.946704186739368e-10</v>
+        <v>2.786452846237353e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.394416692170665e-10</v>
+        <v>1.016143702514682e-08</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.257462051151848e-10</v>
+        <v>5.6351046051617e-10</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.482450935571762e-11</v>
+        <v>1.347017519748306e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.458377862917359e-10</v>
+        <v>2.418164279927026e-10</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.77679462756808e-10</v>
+        <v>9.786861099314592e-09</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.165541135828008e-10</v>
+        <v>4.683730736587677e-09</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.022602502149695e-10</v>
+        <v>1.057637355472707e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.648163688861004e-10</v>
+        <v>9.669072653650801e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.026978849183457e-11</v>
+        <v>1.33264643764619e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.754517642282849e-10</v>
+        <v>3.012702975979664e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.060831449408496e-11</v>
+        <v>1.916981906546766e-09</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.248440405556607e-10</v>
+        <v>4.85755036194746e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.026858707595338e-12</v>
+        <v>3.699316852845413e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.278122495675717e-10</v>
+        <v>6.916015760083383e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.217035999230177e-10</v>
+        <v>2.375149499300733e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.675674599077581e-10</v>
+        <v>1.169915897492046e-08</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.923527224283021e-10</v>
+        <v>1.813591499200129e-10</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.099709626283811e-10</v>
+        <v>2.295480605596367e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.50157622447189e-10</v>
+        <v>1.709815578010421e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.344806181499905e-10</v>
+        <v>2.356769890354826e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.658016584611289e-10</v>
+        <v>1.186233111738488e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.4720330777116e-11</v>
+        <v>6.199117885685723e-10</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.573055713466331e-10</v>
+        <v>3.776397416999089e-09</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.043706398031532e-10</v>
+        <v>5.027653404710009e-09</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.236693968400317e-10</v>
+        <v>1.455934039995554e-09</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.780793984496043e-10</v>
+        <v>4.784549645364677e-09</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.135480598435379e-11</v>
+        <v>9.551355262260586e-09</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.584429059648841e-10</v>
+        <v>2.086213979346496e-10</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.095311757959294e-10</v>
+        <v>2.026564249746343e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>4.313618073847891e-10</v>
+        <v>8.833731968138636e-09</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.015919653430842e-10</v>
+        <v>1.279654826547016e-09</v>
       </c>
       <c r="BL9" t="n">
-        <v>4.758207716726304e-11</v>
+        <v>4.893857319387962e-09</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.200080643863458e-11</v>
+        <v>7.965049064750929e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.919119361319503e-11</v>
+        <v>3.054740238539466e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.468636878776408e-10</v>
+        <v>2.534833454248542e-09</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.512081848620284e-10</v>
+        <v>9.507890474935721e-09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.780600832392622e-12</v>
+        <v>4.027750577506595e-09</v>
       </c>
       <c r="BR9" t="n">
-        <v>6.773121646874714e-11</v>
+        <v>5.954350346115689e-09</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.861713892052478e-12</v>
+        <v>2.036860902165927e-09</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.941763913166255e-11</v>
+        <v>1.977313646150947e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.493218769801132e-10</v>
+        <v>1.277265626598023e-09</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.791887885437831e-11</v>
+        <v>1.145136874214359e-08</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.454809216485444e-10</v>
+        <v>5.108212519644439e-09</v>
       </c>
       <c r="BX9" t="n">
-        <v>2.739812023089261e-11</v>
+        <v>3.048882035727729e-09</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.362517291855994e-10</v>
+        <v>2.613932625905591e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.672786297841512e-11</v>
+        <v>7.774102250834858e-09</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.012436523506466e-10</v>
+        <v>6.333361834975904e-09</v>
       </c>
       <c r="CB9" t="n">
-        <v>1.743686306454606e-10</v>
+        <v>4.872213188455987e-10</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.903011082049488e-11</v>
+        <v>6.483102943377617e-11</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.566362136164791e-11</v>
+        <v>7.02118474471547e-10</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.165500612687609e-10</v>
+        <v>1.013808592631449e-08</v>
       </c>
       <c r="CF9" t="n">
-        <v>5.360718119407082e-11</v>
+        <v>2.099561857704657e-09</v>
       </c>
       <c r="CG9" t="n">
-        <v>4.415876345142955e-11</v>
+        <v>4.997730673750311e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>6.956206444197477e-12</v>
+        <v>4.093854144571196e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.715000273212365e-11</v>
+        <v>7.095219967112598e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.968081667224624e-11</v>
+        <v>2.061553427967766e-10</v>
       </c>
       <c r="CK9" t="n">
-        <v>5.525997021083029e-11</v>
+        <v>2.823352884817609e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.447976877289037e-10</v>
+        <v>2.430925905017034e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.230300167298637e-10</v>
+        <v>5.56362156345358e-09</v>
       </c>
       <c r="CN9" t="n">
-        <v>7.555150949301037e-12</v>
+        <v>6.054335255356591e-09</v>
       </c>
       <c r="CO9" t="n">
-        <v>8.315188815277708e-11</v>
+        <v>1.033741359179885e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.403539506839024e-10</v>
+        <v>1.064983212728521e-09</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.585582941667553e-10</v>
+        <v>5.344061859702265e-10</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.017912837353308e-11</v>
+        <v>4.239418593954269e-09</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.628639445527824e-10</v>
+        <v>5.627426524767998e-09</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.173965534841727e-10</v>
+        <v>2.774522611659336e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>3.042615881465593e-10</v>
+        <v>2.97581026487137e-09</v>
       </c>
       <c r="CV9" t="n">
-        <v>5.757270354900257e-11</v>
+        <v>8.384826721830052e-10</v>
       </c>
       <c r="CW9" t="n">
-        <v>5.930866908698817e-11</v>
+        <v>7.333653684327146e-09</v>
       </c>
       <c r="CX9" t="n">
-        <v>2.26363892907866e-12</v>
+        <v>2.141454347182048e-09</v>
       </c>
       <c r="CY9" t="n">
-        <v>7.441661870055682e-11</v>
+        <v>5.781895850986984e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.235643441206303e-11</v>
+        <v>4.858347946168351e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>5.480399467572283e-11</v>
+        <v>7.811181035322079e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>8.086210173674502e-11</v>
+        <v>8.756804725784662e-10</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.196626387729328e-11</v>
+        <v>2.470139648380609e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.706459973327412e-10</v>
+        <v>2.274209043306996e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>3.27089327845087e-10</v>
+        <v>2.319870073819175e-09</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.276774962479578e-10</v>
+        <v>2.777159169298216e-09</v>
       </c>
       <c r="DG9" t="n">
-        <v>4.006019960201002e-10</v>
+        <v>3.44703865451379e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>4.212301063510893e-10</v>
+        <v>1.555720885448864e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>5.144866754847044e-10</v>
+        <v>1.013527395343772e-08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>6.446815303817743e-11</v>
+        <v>1.243188751942625e-08</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.606244998120232e-11</v>
+        <v>5.939668201726533e-10</v>
       </c>
       <c r="DL9" t="n">
-        <v>7.617772523893507e-10</v>
+        <v>7.558519143913145e-09</v>
       </c>
       <c r="DM9" t="n">
-        <v>3.67400332379475e-10</v>
+        <v>5.121461033041896e-09</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.367673196916996e-10</v>
+        <v>2.648089303391998e-09</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.297177448262744e-10</v>
+        <v>7.361554033025186e-09</v>
       </c>
       <c r="DP9" t="n">
-        <v>1.26478327810986e-10</v>
+        <v>7.237191956832589e-10</v>
       </c>
       <c r="DQ9" t="n">
-        <v>3.853811991749723e-10</v>
+        <v>3.064593023793805e-09</v>
       </c>
       <c r="DR9" t="n">
-        <v>3.198113301960959e-11</v>
+        <v>3.172166140874566e-10</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.151545248045949e-10</v>
+        <v>6.461346568897852e-09</v>
       </c>
       <c r="DT9" t="n">
-        <v>6.174680905468577e-11</v>
+        <v>3.837445916587967e-09</v>
       </c>
       <c r="DU9" t="n">
-        <v>6.457724632813466e-11</v>
+        <v>4.388855501247235e-09</v>
       </c>
       <c r="DV9" t="n">
-        <v>6.951254849507649e-11</v>
+        <v>3.684062499509366e-10</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.790132764245556e-10</v>
+        <v>4.802264363945596e-09</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.361079582373748e-10</v>
+        <v>5.97439697713753e-09</v>
       </c>
       <c r="DY9" t="n">
-        <v>4.317010360299633e-10</v>
+        <v>9.093434449880533e-09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.314080927405925e-10</v>
+        <v>2.080846828178551e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>2.23965929135872e-10</v>
+        <v>4.351548454906151e-09</v>
       </c>
       <c r="EB9" t="n">
-        <v>7.085571018805581e-11</v>
+        <v>3.116037206041256e-09</v>
       </c>
       <c r="EC9" t="n">
-        <v>6.045260125819851e-11</v>
+        <v>4.061438685365459e-10</v>
       </c>
       <c r="ED9" t="n">
-        <v>1.144325745272567e-10</v>
+        <v>6.118930695464542e-09</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.894083778708477e-10</v>
+        <v>4.211619053506865e-09</v>
       </c>
       <c r="EF9" t="n">
-        <v>2.728609005409055e-10</v>
+        <v>4.050471957839363e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>9.425096814119627e-11</v>
+        <v>5.91670179517223e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>8.570168880117635e-11</v>
+        <v>7.967781989748346e-10</v>
       </c>
       <c r="EI9" t="n">
-        <v>1.220489403985781e-10</v>
+        <v>1.738760913028159e-09</v>
       </c>
       <c r="EJ9" t="n">
-        <v>1.596914545043404e-10</v>
+        <v>8.817917063197456e-09</v>
       </c>
       <c r="EK9" t="n">
-        <v>1.697962048741175e-10</v>
+        <v>7.362300546986944e-09</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.048597568306889e-11</v>
+        <v>1.448050568342296e-09</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.529774570907527e-12</v>
+        <v>4.064499015132839e-10</v>
       </c>
       <c r="EN9" t="n">
-        <v>9.919035037775359e-11</v>
+        <v>4.032383038587994e-10</v>
       </c>
       <c r="EO9" t="n">
-        <v>8.868480949608681e-11</v>
+        <v>3.438862306026635e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>1.247968950401912e-10</v>
+        <v>3.904352841033187e-09</v>
       </c>
       <c r="EQ9" t="n">
-        <v>1.506309244003745e-10</v>
+        <v>3.082781585561634e-09</v>
       </c>
       <c r="ER9" t="n">
-        <v>1.585011566440642e-10</v>
+        <v>6.785375816775741e-09</v>
       </c>
       <c r="ES9" t="n">
-        <v>2.349345717966855e-10</v>
+        <v>3.317857988349715e-09</v>
       </c>
       <c r="ET9" t="n">
-        <v>1.005798846986927e-10</v>
+        <v>1.126289617126019e-09</v>
       </c>
       <c r="EU9" t="n">
-        <v>2.10036765757593e-10</v>
+        <v>1.816963801637428e-09</v>
       </c>
       <c r="EV9" t="n">
-        <v>3.418628435891691e-10</v>
+        <v>2.885048200340634e-09</v>
       </c>
       <c r="EW9" t="n">
-        <v>3.556340638644073e-11</v>
+        <v>2.797726272874002e-09</v>
       </c>
       <c r="EX9" t="n">
-        <v>7.933792511849447e-11</v>
+        <v>6.854529166488987e-10</v>
       </c>
       <c r="EY9" t="n">
-        <v>4.411376819390966e-11</v>
+        <v>1.044991293497333e-08</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1.397547876036409e-11</v>
+        <v>2.276616450913593e-09</v>
       </c>
       <c r="FA9" t="n">
-        <v>2.670083945610635e-11</v>
+        <v>5.602906583135336e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>5.303160688363562e-11</v>
+        <v>2.470999849180089e-09</v>
       </c>
       <c r="FC9" t="n">
-        <v>2.950534261358939e-11</v>
+        <v>7.280291924871563e-09</v>
       </c>
       <c r="FD9" t="n">
-        <v>9.143080736961906e-11</v>
+        <v>1.604079924444335e-10</v>
       </c>
       <c r="FE9" t="n">
-        <v>5.809252384691987e-12</v>
+        <v>2.849762426038183e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.915070046987211e-10</v>
+        <v>5.076716824703453e-10</v>
       </c>
       <c r="FG9" t="n">
-        <v>2.798505177592503e-11</v>
+        <v>5.117889445571677e-10</v>
       </c>
       <c r="FH9" t="n">
-        <v>4.801951891675316e-11</v>
+        <v>4.688335941693822e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>3.772857581907374e-10</v>
+        <v>8.164887432826617e-09</v>
       </c>
       <c r="FJ9" t="n">
-        <v>3.127055836493753e-10</v>
+        <v>1.836799601306893e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>1.189350840036241e-10</v>
+        <v>1.923785797330879e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>3.513095370166752e-10</v>
+        <v>6.270942876085428e-09</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.028941098990543e-10</v>
+        <v>2.674428178917054e-10</v>
       </c>
       <c r="FN9" t="n">
-        <v>3.156073180576868e-10</v>
+        <v>6.554286002824483e-09</v>
       </c>
       <c r="FO9" t="n">
-        <v>3.608200405125217e-10</v>
+        <v>8.648035176861413e-09</v>
       </c>
       <c r="FP9" t="n">
-        <v>1.451436609789525e-10</v>
+        <v>8.501074511002571e-09</v>
       </c>
       <c r="FQ9" t="n">
-        <v>2.547125010909923e-11</v>
+        <v>7.635064136479741e-09</v>
       </c>
       <c r="FR9" t="n">
-        <v>4.285269639137113e-10</v>
+        <v>1.357596968176722e-08</v>
       </c>
       <c r="FS9" t="n">
-        <v>3.491691380475004e-10</v>
+        <v>8.581189980816362e-09</v>
       </c>
       <c r="FT9" t="n">
-        <v>3.348402666247807e-10</v>
+        <v>1.121839177109507e-09</v>
       </c>
       <c r="FU9" t="n">
-        <v>1.579856245825795e-10</v>
+        <v>6.927312057314339e-10</v>
       </c>
       <c r="FV9" t="n">
-        <v>1.670632659989124e-10</v>
+        <v>1.449157793764755e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>7.877965640945561e-11</v>
+        <v>9.496719854951152e-09</v>
       </c>
       <c r="FX9" t="n">
-        <v>9.796199962330832e-11</v>
+        <v>1.671906835198911e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>2.487227368508371e-10</v>
+        <v>2.098771378911124e-09</v>
       </c>
       <c r="FZ9" t="n">
-        <v>4.207606207895509e-10</v>
+        <v>5.995381968659785e-10</v>
       </c>
       <c r="GA9" t="n">
-        <v>1.873202565283449e-10</v>
+        <v>8.650861360592899e-09</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.948531891393657e-10</v>
+        <v>2.811441524031011e-09</v>
       </c>
       <c r="GC9" t="n">
-        <v>3.681468740968086e-10</v>
+        <v>1.228935264663278e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>1.272211502811871e-12</v>
+        <v>9.889638441507032e-09</v>
       </c>
       <c r="GE9" t="n">
-        <v>2.613165586695665e-11</v>
+        <v>3.087143873869991e-09</v>
       </c>
       <c r="GF9" t="n">
-        <v>3.306583895579251e-10</v>
+        <v>3.849098373365223e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>9.497055225571316e-11</v>
+        <v>3.94390686775381e-10</v>
       </c>
     </row>
   </sheetData>
